--- a/excel/2. Perturbation 5.xlsx
+++ b/excel/2. Perturbation 5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\2. Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\git\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DF5AAC-A624-4F07-8820-050B1C72DE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CC4FB6-92A2-408C-BE4A-5553BF2D67EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{88C08D68-2E9A-4EC7-8AF8-2F1D08621B1E}"/>
   </bookViews>
@@ -442,7 +442,7 @@
     <t>Perturbation</t>
   </si>
   <si>
-    <t>Alpha-5% &amp; Beta+5% but capped at 0 and 1 respectively</t>
+    <t>lower bounds -5% &amp; upper bounds +5% but capped at 0 and 1 respectively</t>
   </si>
 </sst>
 </file>
@@ -549,12 +549,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -974,21 +974,6 @@
         <color indexed="64"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color rgb="FFD6DADC"/>
       </right>
       <top style="medium">
@@ -1263,81 +1248,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FFFF0000"/>
       </left>
@@ -1382,11 +1292,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1525,7 +1450,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1548,7 +1472,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1566,7 +1490,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1578,7 +1502,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1590,22 +1514,22 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1614,10 +1538,95 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1632,112 +1641,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1971,28 +1877,28 @@
                   <c:v>MailNews Core</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Mozilla QA</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>NSS</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Release Engineering</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Remote Protocol</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>support.mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>WebExtensions</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>Webtools</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Mozilla QA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2004,52 +1910,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>8.8931533443666486E-2</c:v>
+                  <c:v>9.3069042245856021E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25092729532770469</c:v>
+                  <c:v>0.24510450258306007</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3255512805040576E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.10548048879098604</c:v>
+                  <c:v>9.5554371204441171E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.17199074843805262</c:v>
+                  <c:v>0.1792512868795505</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2063617157585256E-2</c:v>
+                  <c:v>7.3131370946117324E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.5768711170631359E-2</c:v>
+                  <c:v>1.9694686569376348E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.3651923350756014E-3</c:v>
+                  <c:v>6.3853006314624075E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.23264172429957472</c:v>
+                  <c:v>0.13253305131736207</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.23625706359728077</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.12659733841535062</c:v>
+                  <c:v>5.1098760368070246E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.4782518596586777E-2</c:v>
+                  <c:v>0.12055679783934356</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.11028135745546304</c:v>
+                  <c:v>6.1587739956845307E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.4434750694249968E-2</c:v>
+                  <c:v>9.5155337659253381E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.3437329151276978E-2</c:v>
+                  <c:v>2.2910994333440109E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.14932866403198614</c:v>
+                  <c:v>4.6286262883317296E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2107,7 +2013,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F149FF77-2CBD-4AB4-993E-5285D290DC93}" type="CELLRANGE">
+                    <a:fld id="{709F09E3-6DD6-444D-8A45-7A6D5B24E71C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2139,7 +2045,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1C6F56B8-6076-4298-B9D6-1631FA55023A}" type="CELLRANGE">
+                    <a:fld id="{A9178E2B-C560-476D-BBDF-FEEEDDB19B58}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2172,7 +2078,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D373D127-A662-413A-9D3A-58CE2FC26F45}" type="CELLRANGE">
+                    <a:fld id="{0F3AF1A6-0DBE-4211-8B9C-6A371F78BBF2}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2205,7 +2111,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{70B8BC40-102E-4959-8A3E-1D0CC393DBB1}" type="CELLRANGE">
+                    <a:fld id="{B5582D99-B11D-489D-9601-65AC1C13FC5B}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2238,7 +2144,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D3A7F5ED-42C8-4BF4-BC22-4D929C7154EF}" type="CELLRANGE">
+                    <a:fld id="{82A8F4E6-A86D-4837-AE49-2748EF2985BA}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2271,7 +2177,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AD23CE34-352C-44D9-9613-10B3A8CE55C4}" type="CELLRANGE">
+                    <a:fld id="{B8BDA2C8-B020-4B48-9DBA-9B6BCFA8F6B9}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2304,7 +2210,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F8A6D6B5-9E40-4A41-90C9-6CF4F8CA072B}" type="CELLRANGE">
+                    <a:fld id="{FF92A1CF-EA5E-417D-A492-96D93B24E387}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2337,7 +2243,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9E492E04-0386-4676-ADEE-B93936B240C4}" type="CELLRANGE">
+                    <a:fld id="{4BAE429C-1F29-4078-871C-2D8D5D835F94}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2370,7 +2276,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BBCA7BB1-577C-4EEF-8B08-B7AF546B9B7E}" type="CELLRANGE">
+                    <a:fld id="{8312B11F-B67D-4690-B459-5554039CC168}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2403,7 +2309,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3664E9D0-D963-474F-A30F-6DC40BBDFEF7}" type="CELLRANGE">
+                    <a:fld id="{5CEF3D7C-02DA-4C8B-AE1E-C3E8DF76F2E9}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2436,7 +2342,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D6E6383B-D6FD-492F-8725-A21446B1B050}" type="CELLRANGE">
+                    <a:fld id="{B69451DE-3F54-435C-9B19-DD174AB55386}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2469,7 +2375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0B125D1D-5FCC-4D6E-A42B-6AC8D307FB8F}" type="CELLRANGE">
+                    <a:fld id="{0B0806DD-83D5-45D3-9AF2-CFBBB9FCE8EF}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2502,7 +2408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4E140D5E-16BC-483E-90AE-B10E09899819}" type="CELLRANGE">
+                    <a:fld id="{D26589BD-16A5-4A1F-A6A9-69F4593A5823}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2535,7 +2441,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{67A17922-C8FE-4012-A665-B4EB04DFEEA6}" type="CELLRANGE">
+                    <a:fld id="{4669F3E7-F5E6-4B75-B5D1-9B65CB4D250E}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2568,7 +2474,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1615C1DC-F089-44F7-A090-E2DACBDB1EC4}" type="CELLRANGE">
+                    <a:fld id="{77DC0294-D759-4CBF-99F3-167B7EF19E45}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2601,7 +2507,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C8B3CC33-3A71-4166-9AC8-98A901B5FB0A}" type="CELLRANGE">
+                    <a:fld id="{682521B4-3B24-4875-9625-87EBFF6A3933}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2714,28 +2620,28 @@
                   <c:v>MailNews Core</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Mozilla QA</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>NSS</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Release Engineering</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Remote Protocol</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>support.mozilla.org</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>WebExtensions</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>Webtools</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Mozilla QA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2747,52 +2653,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.75085381879789037</c:v>
+                  <c:v>0.70432973956055833</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.54523536145147133</c:v>
+                  <c:v>0.43798342964748282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.67977626405311609</c:v>
+                  <c:v>0.5979623177074187</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.75797159370657774</c:v>
+                  <c:v>0.69665040946444801</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6340613426272208</c:v>
+                  <c:v>0.54303689213901918</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.75236196600498573</c:v>
+                  <c:v>0.71253055825164124</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.67616906063388638</c:v>
+                  <c:v>0.61852080749544647</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.71878167390263936</c:v>
+                  <c:v>0.72845062116586545</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.77483080840311114</c:v>
+                  <c:v>0.62882429274703289</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.74006417316866091</c:v>
+                  <c:v>0.75865581156430628</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.65172457365413328</c:v>
+                  <c:v>0.67559318872934293</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.68282183253167106</c:v>
+                  <c:v>0.5720843422545111</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.78293102626360278</c:v>
+                  <c:v>0.59888955827293278</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.60346860794955037</c:v>
+                  <c:v>0.75798795005442132</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.78601276296757072</c:v>
+                  <c:v>0.50171138542018112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2805,52 +2711,52 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="16"/>
                   <c:pt idx="0">
-                    <c:v>0.751</c:v>
+                    <c:v>0.704</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>1.000</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>0.545</c:v>
+                    <c:v>0.438</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>0.680</c:v>
+                    <c:v>0.598</c:v>
                   </c:pt>
                   <c:pt idx="4">
+                    <c:v>0.697</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.543</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.713</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>0.619</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0.728</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>0.629</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>0.759</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>0.676</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>0.572</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>0.599</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
                     <c:v>0.758</c:v>
                   </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0.634</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0.752</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>0.676</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>0.719</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>0.775</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>0.740</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>0.652</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>0.683</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>0.783</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>0.603</c:v>
-                  </c:pt>
                   <c:pt idx="15">
-                    <c:v>0.786</c:v>
+                    <c:v>0.502</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -4021,26 +3927,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="66"/>
-      <c r="C1" s="66" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="20"/>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="61" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4051,10 +3957,10 @@
       <c r="C4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="62">
         <v>45170</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="62">
         <v>45199</v>
       </c>
       <c r="F4" s="8">
@@ -4068,10 +3974,10 @@
       <c r="C5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="62">
         <v>45200</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="62">
         <v>45230</v>
       </c>
       <c r="F5" s="8">
@@ -4085,10 +3991,10 @@
       <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="62">
         <v>45231</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="62">
         <v>45260</v>
       </c>
       <c r="F6" s="8">
@@ -4102,10 +4008,10 @@
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="62">
         <v>45261</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="62">
         <v>45291</v>
       </c>
       <c r="F7" s="8">
@@ -4119,10 +4025,10 @@
       <c r="C8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="62">
         <v>45292</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="62">
         <v>45322</v>
       </c>
       <c r="F8" s="8">
@@ -4136,10 +4042,10 @@
       <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="62">
         <v>45323</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="62">
         <v>45351</v>
       </c>
       <c r="F9" s="8">
@@ -4153,10 +4059,10 @@
       <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="62">
         <v>45352</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="62">
         <v>45382</v>
       </c>
       <c r="F10" s="8">
@@ -4170,10 +4076,10 @@
       <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="62">
         <v>45383</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="62">
         <v>45412</v>
       </c>
       <c r="F11" s="8">
@@ -4187,10 +4093,10 @@
       <c r="C12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="62">
         <v>45413</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="62">
         <v>45443</v>
       </c>
       <c r="F12" s="8">
@@ -4204,10 +4110,10 @@
       <c r="C13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="62">
         <v>45444</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="62">
         <v>45473</v>
       </c>
       <c r="F13" s="8">
@@ -4221,10 +4127,10 @@
       <c r="C14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="62">
         <v>45474</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="62">
         <v>45504</v>
       </c>
       <c r="F14" s="8">
@@ -4238,10 +4144,10 @@
       <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="62">
         <v>45505</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="62">
         <v>45535</v>
       </c>
       <c r="F15" s="8">
@@ -4252,10 +4158,10 @@
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="5:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="64" t="s">
+      <c r="E17" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="64">
         <f>SUM(F4:F15)</f>
         <v>8484</v>
       </c>
@@ -5946,94 +5852,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="T1" s="92" t="s">
+      <c r="T1" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="92"/>
-      <c r="Z1" s="92"/>
-      <c r="AA1" s="92"/>
-      <c r="AB1" s="92"/>
-      <c r="AC1" s="92"/>
-      <c r="AD1" s="92"/>
-      <c r="AF1" s="92" t="s">
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="138"/>
+      <c r="Y1" s="138"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="138"/>
+      <c r="AB1" s="138"/>
+      <c r="AC1" s="138"/>
+      <c r="AD1" s="138"/>
+      <c r="AF1" s="138" t="s">
         <v>130</v>
       </c>
-      <c r="AG1" s="92"/>
-      <c r="AH1" s="92"/>
-      <c r="AI1" s="92"/>
-      <c r="AJ1" s="92"/>
-      <c r="AK1" s="92"/>
-      <c r="AL1" s="92"/>
-      <c r="AM1" s="92"/>
-      <c r="AN1" s="92"/>
-      <c r="AO1" s="92"/>
-      <c r="AP1" s="92"/>
-      <c r="AQ1" s="92"/>
-      <c r="AR1" s="92"/>
-      <c r="AS1" s="92"/>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
-      <c r="BB1" s="92"/>
-      <c r="BC1" s="92"/>
-      <c r="BD1" s="92"/>
-      <c r="BE1" s="92"/>
-      <c r="BF1" s="92"/>
-      <c r="BG1" s="92"/>
-      <c r="BH1" s="92"/>
-      <c r="BI1" s="92"/>
-      <c r="BJ1" s="92"/>
-      <c r="BK1" s="92"/>
-      <c r="BL1" s="92"/>
-      <c r="BM1" s="92"/>
-      <c r="BN1" s="92"/>
-      <c r="BO1" s="92"/>
-      <c r="BP1" s="92"/>
-      <c r="BQ1" s="92"/>
-      <c r="BR1" s="92"/>
-      <c r="BS1" s="92"/>
-      <c r="BT1" s="92"/>
-      <c r="BU1" s="92"/>
-      <c r="BV1" s="92"/>
-      <c r="BW1" s="92"/>
-      <c r="BX1" s="92"/>
-      <c r="BY1" s="92"/>
-      <c r="BZ1" s="92"/>
-      <c r="CA1" s="92"/>
-      <c r="CB1" s="92"/>
-      <c r="CC1" s="92"/>
-      <c r="CD1" s="92"/>
-      <c r="CE1" s="92"/>
-      <c r="CF1" s="92"/>
-      <c r="CG1" s="92"/>
-      <c r="CH1" s="92"/>
-      <c r="CI1" s="92"/>
-      <c r="CJ1" s="92"/>
-      <c r="CK1" s="92"/>
-      <c r="CL1" s="92"/>
-      <c r="CM1" s="92"/>
-      <c r="CO1" s="91" t="s">
+      <c r="AG1" s="138"/>
+      <c r="AH1" s="138"/>
+      <c r="AI1" s="138"/>
+      <c r="AJ1" s="138"/>
+      <c r="AK1" s="138"/>
+      <c r="AL1" s="138"/>
+      <c r="AM1" s="138"/>
+      <c r="AN1" s="138"/>
+      <c r="AO1" s="138"/>
+      <c r="AP1" s="138"/>
+      <c r="AQ1" s="138"/>
+      <c r="AR1" s="138"/>
+      <c r="AS1" s="138"/>
+      <c r="AT1" s="138"/>
+      <c r="AU1" s="138"/>
+      <c r="AV1" s="138"/>
+      <c r="AW1" s="138"/>
+      <c r="AX1" s="138"/>
+      <c r="AY1" s="138"/>
+      <c r="AZ1" s="138"/>
+      <c r="BA1" s="138"/>
+      <c r="BB1" s="138"/>
+      <c r="BC1" s="138"/>
+      <c r="BD1" s="138"/>
+      <c r="BE1" s="138"/>
+      <c r="BF1" s="138"/>
+      <c r="BG1" s="138"/>
+      <c r="BH1" s="138"/>
+      <c r="BI1" s="138"/>
+      <c r="BJ1" s="138"/>
+      <c r="BK1" s="138"/>
+      <c r="BL1" s="138"/>
+      <c r="BM1" s="138"/>
+      <c r="BN1" s="138"/>
+      <c r="BO1" s="138"/>
+      <c r="BP1" s="138"/>
+      <c r="BQ1" s="138"/>
+      <c r="BR1" s="138"/>
+      <c r="BS1" s="138"/>
+      <c r="BT1" s="138"/>
+      <c r="BU1" s="138"/>
+      <c r="BV1" s="138"/>
+      <c r="BW1" s="138"/>
+      <c r="BX1" s="138"/>
+      <c r="BY1" s="138"/>
+      <c r="BZ1" s="138"/>
+      <c r="CA1" s="138"/>
+      <c r="CB1" s="138"/>
+      <c r="CC1" s="138"/>
+      <c r="CD1" s="138"/>
+      <c r="CE1" s="138"/>
+      <c r="CF1" s="138"/>
+      <c r="CG1" s="138"/>
+      <c r="CH1" s="138"/>
+      <c r="CI1" s="138"/>
+      <c r="CJ1" s="138"/>
+      <c r="CK1" s="138"/>
+      <c r="CL1" s="138"/>
+      <c r="CM1" s="138"/>
+      <c r="CO1" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="CP1" s="91"/>
-      <c r="CQ1" s="91"/>
-      <c r="CR1" s="91"/>
-      <c r="CS1" s="91"/>
+      <c r="CP1" s="137"/>
+      <c r="CQ1" s="137"/>
+      <c r="CR1" s="137"/>
+      <c r="CS1" s="137"/>
       <c r="CW1" s="52" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="65" t="s">
         <v>127</v>
       </c>
       <c r="H2" t="s">
@@ -6045,7 +5951,7 @@
       <c r="AF2" t="s">
         <v>54</v>
       </c>
-      <c r="AL2" s="66" t="s">
+      <c r="AL2" s="65" t="s">
         <v>128</v>
       </c>
       <c r="AR2" t="s">
@@ -6074,22 +5980,22 @@
       </c>
     </row>
     <row r="3" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="68" t="s">
         <v>51</v>
       </c>
       <c r="H3" s="26" t="s">
@@ -6125,27 +6031,27 @@
       <c r="R3" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="103" t="s">
+      <c r="T3" s="110" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="104" t="s">
+      <c r="U3" s="111" t="s">
         <v>64</v>
       </c>
-      <c r="V3" s="104" t="s">
+      <c r="V3" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="W3" s="104" t="s">
+      <c r="W3" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="X3" s="104" t="s">
+      <c r="X3" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="Y3" s="105"/>
-      <c r="Z3" s="105"/>
-      <c r="AA3" s="105"/>
-      <c r="AB3" s="105"/>
-      <c r="AC3" s="105"/>
-      <c r="AD3" s="106"/>
+      <c r="Y3" s="121"/>
+      <c r="Z3" s="121"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="121"/>
+      <c r="AC3" s="121"/>
+      <c r="AD3" s="122"/>
       <c r="AF3" s="27"/>
       <c r="AG3" s="28" t="s">
         <v>64</v>
@@ -6160,7 +6066,7 @@
         <v>67</v>
       </c>
       <c r="AK3" s="30"/>
-      <c r="AL3" s="67" t="s">
+      <c r="AL3" s="66" t="s">
         <v>48</v>
       </c>
       <c r="AM3" s="31" t="s">
@@ -6210,36 +6116,36 @@
       </c>
       <c r="BC3" s="12"/>
       <c r="BD3" s="15"/>
-      <c r="BE3" s="93" t="s">
+      <c r="BE3" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="BF3" s="93"/>
-      <c r="BG3" s="93"/>
-      <c r="BH3" s="93"/>
-      <c r="BI3" s="93" t="s">
+      <c r="BF3" s="139"/>
+      <c r="BG3" s="139"/>
+      <c r="BH3" s="139"/>
+      <c r="BI3" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="BJ3" s="93"/>
-      <c r="BK3" s="93"/>
-      <c r="BL3" s="94"/>
+      <c r="BJ3" s="139"/>
+      <c r="BK3" s="139"/>
+      <c r="BL3" s="140"/>
       <c r="BM3" s="12"/>
       <c r="BN3" s="12"/>
-      <c r="BP3" s="133" t="s">
+      <c r="BP3" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="BQ3" s="133"/>
-      <c r="BR3" s="133" t="s">
+      <c r="BQ3" s="130"/>
+      <c r="BR3" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="133"/>
-      <c r="BT3" s="133" t="s">
+      <c r="BS3" s="130"/>
+      <c r="BT3" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="BU3" s="133"/>
-      <c r="BV3" s="133" t="s">
+      <c r="BU3" s="130"/>
+      <c r="BV3" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="BW3" s="133"/>
+      <c r="BW3" s="130"/>
       <c r="BY3" s="37" t="s">
         <v>74</v>
       </c>
@@ -6262,10 +6168,10 @@
       <c r="CM3" t="s">
         <v>78</v>
       </c>
-      <c r="CP3" s="90" t="s">
+      <c r="CP3" s="130" t="s">
         <v>79</v>
       </c>
-      <c r="CQ3" s="90"/>
+      <c r="CQ3" s="130"/>
       <c r="CR3" t="s">
         <v>80</v>
       </c>
@@ -6280,19 +6186,19 @@
       <c r="A4" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="71">
+      <c r="B4" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="70">
         <v>6</v>
       </c>
-      <c r="D4" s="71">
+      <c r="D4" s="70">
         <v>32</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="70">
         <v>2</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="71">
         <v>0</v>
       </c>
       <c r="H4" s="39" t="s">
@@ -6328,33 +6234,33 @@
       <c r="R4" s="23">
         <v>0</v>
       </c>
-      <c r="T4" s="107" t="s">
+      <c r="T4" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="108">
+      <c r="U4" s="113">
         <v>2</v>
       </c>
-      <c r="V4" s="108">
+      <c r="V4" s="113">
         <v>14</v>
       </c>
-      <c r="W4" s="108">
-        <v>0</v>
-      </c>
-      <c r="X4" s="108">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="109"/>
-      <c r="Z4" s="109"/>
-      <c r="AA4" s="109" t="s">
+      <c r="W4" s="113">
+        <v>0</v>
+      </c>
+      <c r="X4" s="113">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114" t="s">
         <v>87</v>
       </c>
-      <c r="AB4" s="109" t="s">
+      <c r="AB4" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="AC4" s="109" t="s">
+      <c r="AC4" s="114" t="s">
         <v>89</v>
       </c>
-      <c r="AD4" s="110" t="s">
+      <c r="AD4" s="123" t="s">
         <v>90</v>
       </c>
       <c r="AF4" s="40" t="s">
@@ -6379,19 +6285,19 @@
       <c r="AL4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM4" s="77">
+      <c r="AM4" s="76">
         <f t="shared" ref="AM4:AM35" si="0">(AG$4-C4)/(AG$4-AG$5)</f>
         <v>0.98070739549839225</v>
       </c>
-      <c r="AN4" s="78">
+      <c r="AN4" s="77">
         <f t="shared" ref="AN4:AN35" si="1">(D4-AH$5)/(AH$4-AH$5)</f>
         <v>0.1807909604519774</v>
       </c>
-      <c r="AO4" s="78">
+      <c r="AO4" s="77">
         <f t="shared" ref="AO4:AO35" si="2">(E4-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP4" s="79">
+      <c r="AP4" s="78">
         <f t="shared" ref="AP4:AP35" si="3">(AJ$4-F4)/(AJ$4-AJ$5)</f>
         <v>1</v>
       </c>
@@ -6457,37 +6363,37 @@
       <c r="BM4" s="45"/>
       <c r="BN4" s="45"/>
       <c r="BO4" s="30"/>
-      <c r="BP4" s="139">
+      <c r="BP4" s="103">
         <f>AA37</f>
-        <v>0</v>
-      </c>
-      <c r="BQ4" s="140">
+        <v>1.4074074074074074E-2</v>
+      </c>
+      <c r="BQ4" s="104">
         <f>AA38</f>
-        <v>0.15227272727272728</v>
-      </c>
-      <c r="BR4" s="140">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BR4" s="104">
         <f>AA39</f>
-        <v>6.363636363636363E-2</v>
-      </c>
-      <c r="BS4" s="140">
+        <v>7.0370370370370361E-2</v>
+      </c>
+      <c r="BS4" s="104">
         <f>AA40</f>
-        <v>0.36818181818181817</v>
-      </c>
-      <c r="BT4" s="137">
+        <v>0.21777777777777779</v>
+      </c>
+      <c r="BT4" s="104">
         <f>AB37</f>
-        <v>0.34772727272727272</v>
-      </c>
-      <c r="BU4" s="137">
+        <v>0.38218390804597702</v>
+      </c>
+      <c r="BU4" s="104">
         <f>AB38</f>
-        <v>0.59545454545454546</v>
-      </c>
-      <c r="BV4" s="137">
+        <v>0.57931034482758625</v>
+      </c>
+      <c r="BV4" s="104">
         <f>AB39</f>
-        <v>0.17727272727272725</v>
-      </c>
-      <c r="BW4" s="138">
+        <v>0.21839080459770113</v>
+      </c>
+      <c r="BW4" s="105">
         <f>AB40</f>
-        <v>0.42499999999999999</v>
+        <v>0.39827586206896554</v>
       </c>
       <c r="BY4" s="37" t="s">
         <v>91</v>
@@ -6496,46 +6402,46 @@
       <c r="CA4" s="2"/>
       <c r="CB4" s="2"/>
       <c r="CC4" s="2"/>
-      <c r="CI4" s="141" t="s">
-        <v>1</v>
-      </c>
-      <c r="CJ4" s="142">
-        <f t="shared" ref="CJ4:CJ19" si="4">(BZ6+CD6+BZ23+CD23)/$T$41</f>
-        <v>2.7077249449902474E-2</v>
-      </c>
-      <c r="CK4" s="143">
-        <f t="shared" ref="CK4:CK19" si="5">(CA6+CE6+CA23+CE23)/$T$41</f>
-        <v>0.29291429475065051</v>
-      </c>
-      <c r="CL4" s="143">
-        <f t="shared" ref="CL4:CL19" si="6">(CB6+CF6+CB23+CF23)/$T$41</f>
-        <v>4.4568848376605172E-2</v>
-      </c>
-      <c r="CM4" s="144">
-        <f t="shared" ref="CM4:CM19" si="7">(CC6+CG6+CC23+CG23)/$T$41</f>
-        <v>0.33806626979446824</v>
-      </c>
-      <c r="CO4" s="141" t="s">
-        <v>1</v>
-      </c>
-      <c r="CP4" s="142">
-        <f t="shared" ref="CP4:CP19" si="8">CJ4-CM4</f>
-        <v>-0.31098902034456577</v>
-      </c>
-      <c r="CQ4" s="143">
-        <f t="shared" ref="CQ4:CQ19" si="9">CK4-CL4</f>
-        <v>0.24834544637404532</v>
-      </c>
-      <c r="CR4" s="151">
-        <f t="shared" ref="CR4:CS19" si="10">(CP4+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>8.8931533443666486E-2</v>
-      </c>
-      <c r="CS4" s="152">
-        <f t="shared" si="10"/>
-        <v>0.75085381879789037</v>
+      <c r="CI4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="CJ4" s="14">
+        <f t="shared" ref="CJ4:CM11" si="4">(BZ6+CD6+BZ23+CD23)/$T$41</f>
+        <v>3.1764303692242139E-2</v>
+      </c>
+      <c r="CK4" s="14">
+        <f t="shared" si="4"/>
+        <v>0.24378329484750913</v>
+      </c>
+      <c r="CL4" s="14">
+        <f t="shared" si="4"/>
+        <v>6.3638815894820192E-2</v>
+      </c>
+      <c r="CM4" s="14">
+        <f t="shared" si="4"/>
+        <v>0.28789861811396289</v>
+      </c>
+      <c r="CO4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="CP4" s="14">
+        <f t="shared" ref="CP4:CP19" si="5">CJ4-CM4</f>
+        <v>-0.25613431442172074</v>
+      </c>
+      <c r="CQ4" s="14">
+        <f t="shared" ref="CQ4:CQ19" si="6">CK4-CL4</f>
+        <v>0.18014447895268892</v>
+      </c>
+      <c r="CR4" s="49">
+        <f t="shared" ref="CR4:CS19" si="7">(CP4+$CP$21)/($CP$21+$CQ$21)</f>
+        <v>9.3069042245856021E-2</v>
+      </c>
+      <c r="CS4" s="49">
+        <f t="shared" si="7"/>
+        <v>0.70432973956055833</v>
       </c>
       <c r="CU4" s="14"/>
-      <c r="CW4" s="156">
+      <c r="CW4" s="106">
         <f>RANK(CR4,$CR$4:$CR$19,0)</f>
         <v>8</v>
       </c>
@@ -6593,33 +6499,33 @@
       <c r="R5" s="23">
         <v>0</v>
       </c>
-      <c r="T5" s="107" t="s">
+      <c r="T5" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="U5" s="108">
+      <c r="U5" s="113">
         <v>3</v>
       </c>
-      <c r="V5" s="108">
+      <c r="V5" s="113">
         <v>31</v>
       </c>
-      <c r="W5" s="108">
-        <v>0</v>
-      </c>
-      <c r="X5" s="108">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="109"/>
-      <c r="Z5" s="109"/>
-      <c r="AA5" s="109" t="s">
+      <c r="W5" s="113">
+        <v>0</v>
+      </c>
+      <c r="X5" s="113">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114" t="s">
         <v>93</v>
       </c>
-      <c r="AB5" s="109" t="s">
+      <c r="AB5" s="114" t="s">
         <v>94</v>
       </c>
-      <c r="AC5" s="111" t="s">
+      <c r="AC5" s="124" t="s">
         <v>95</v>
       </c>
-      <c r="AD5" s="110" t="s">
+      <c r="AD5" s="123" t="s">
         <v>96</v>
       </c>
       <c r="AF5" s="40" t="s">
@@ -6656,7 +6562,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP5" s="80">
+      <c r="AP5" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6702,15 +6608,15 @@
         <v>0.53697749196141475</v>
       </c>
       <c r="BF5" s="13">
-        <f t="shared" ref="BF5:BH20" si="11">MIN(AN4,AN20,AN36,AN52,AN68,AN84)</f>
+        <f t="shared" ref="BF5:BH20" si="8">MIN(AN4,AN20,AN36,AN52,AN68,AN84)</f>
         <v>0.1807909604519774</v>
       </c>
       <c r="BG5" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH5" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BI5" s="13">
@@ -6718,36 +6624,36 @@
         <v>0.98713826366559487</v>
       </c>
       <c r="BJ5" s="13">
-        <f t="shared" ref="BJ5:BL20" si="12">MAX(AN4,AN20,AN36,AN52,AN68,AN84)</f>
+        <f t="shared" ref="BJ5:BL20" si="9">MAX(AN4,AN20,AN36,AN52,AN68,AN84)</f>
         <v>0.60451977401129942</v>
       </c>
       <c r="BK5" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.23076923076923078</v>
       </c>
       <c r="BL5" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM5" s="45"/>
       <c r="BN5" s="45"/>
       <c r="BO5" s="30"/>
-      <c r="BP5" s="134" t="s">
+      <c r="BP5" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="BQ5" s="135"/>
-      <c r="BR5" s="134" t="s">
+      <c r="BQ5" s="132"/>
+      <c r="BR5" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="BS5" s="135"/>
-      <c r="BT5" s="134" t="s">
+      <c r="BS5" s="132"/>
+      <c r="BT5" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="BU5" s="135"/>
-      <c r="BV5" s="134" t="s">
+      <c r="BU5" s="132"/>
+      <c r="BV5" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="BW5" s="135"/>
+      <c r="BW5" s="132"/>
       <c r="BY5" s="38"/>
       <c r="BZ5" s="51" t="s">
         <v>97</v>
@@ -6773,47 +6679,47 @@
       <c r="CG5" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="CI5" s="141" t="s">
+      <c r="CI5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="CJ5" s="145">
+      <c r="CJ5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9664807614339985E-2</v>
-      </c>
-      <c r="CK5" s="146">
+        <v>2.7828579811772808E-2</v>
+      </c>
+      <c r="CK5" s="14">
+        <f t="shared" si="4"/>
+        <v>0.40248871144163573</v>
+      </c>
+      <c r="CL5" s="14">
+        <f t="shared" si="4"/>
+        <v>1.1313709787427236E-2</v>
+      </c>
+      <c r="CM5" s="14">
+        <f t="shared" si="4"/>
+        <v>0.17544970587142725</v>
+      </c>
+      <c r="CO5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="CP5" s="14">
         <f t="shared" si="5"/>
-        <v>0.4682089601557119</v>
-      </c>
-      <c r="CL5" s="146">
+        <v>-0.14762112605965444</v>
+      </c>
+      <c r="CQ5" s="14">
         <f t="shared" si="6"/>
-        <v>9.3311756491245047E-3</v>
-      </c>
-      <c r="CM5" s="147">
+        <v>0.39117500165420849</v>
+      </c>
+      <c r="CR5" s="49">
         <f t="shared" si="7"/>
-        <v>0.19376492862898773</v>
-      </c>
-      <c r="CO5" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="CP5" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.17410012101464775</v>
-      </c>
-      <c r="CQ5" s="146">
-        <f t="shared" si="9"/>
-        <v>0.45887778450658739</v>
-      </c>
-      <c r="CR5" s="49">
-        <f t="shared" si="10"/>
-        <v>0.25092729532770469</v>
-      </c>
-      <c r="CS5" s="153">
-        <f t="shared" si="10"/>
+        <v>0.24510450258306007</v>
+      </c>
+      <c r="CS5" s="49">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="CU5" s="14"/>
-      <c r="CW5" s="157">
-        <f t="shared" ref="CW5:CW19" si="13">RANK(CR5,$CR$4:$CR$19,0)</f>
+      <c r="CW5" s="107">
+        <f t="shared" ref="CW5:CW19" si="10">RANK(CR5,$CR$4:$CR$19,0)</f>
         <v>1</v>
       </c>
       <c r="CY5" s="14"/>
@@ -6870,33 +6776,33 @@
       <c r="R6" s="23">
         <v>1</v>
       </c>
-      <c r="T6" s="107" t="s">
+      <c r="T6" s="112" t="s">
         <v>37</v>
       </c>
-      <c r="U6" s="108">
+      <c r="U6" s="113">
         <v>4</v>
       </c>
-      <c r="V6" s="108">
+      <c r="V6" s="113">
         <v>31</v>
       </c>
-      <c r="W6" s="108">
-        <v>1</v>
-      </c>
-      <c r="X6" s="108">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="109"/>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="109" t="s">
+      <c r="W6" s="113">
+        <v>1</v>
+      </c>
+      <c r="X6" s="113">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114" t="s">
         <v>103</v>
       </c>
-      <c r="AB6" s="109" t="s">
+      <c r="AB6" s="114" t="s">
         <v>104</v>
       </c>
-      <c r="AC6" s="109" t="s">
+      <c r="AC6" s="114" t="s">
         <v>105</v>
       </c>
-      <c r="AD6" s="110" t="s">
+      <c r="AD6" s="123" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="17"/>
@@ -6927,7 +6833,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="80">
+      <c r="AP6" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6969,35 +6875,35 @@
         <v>2</v>
       </c>
       <c r="BE6" s="13">
-        <f t="shared" ref="BE6:BE20" si="14">MIN(AM5,AM21,AM37,AM53,AM69,AM85)</f>
+        <f t="shared" ref="BE6:BE20" si="11">MIN(AM5,AM21,AM37,AM53,AM69,AM85)</f>
         <v>0.99356913183279738</v>
       </c>
       <c r="BF6" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="BG6" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BH6" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="BI6" s="13">
-        <f t="shared" ref="BI6:BI20" si="15">MAX(AM5,AM21,AM37,AM53,AM69,AM85)</f>
+        <f t="shared" ref="BI6:BI20" si="12">MAX(AM5,AM21,AM37,AM53,AM69,AM85)</f>
         <v>1</v>
       </c>
       <c r="BJ6" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.81355932203389836</v>
       </c>
       <c r="BK6" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BL6" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM6" s="45"/>
@@ -7032,78 +6938,78 @@
       </c>
       <c r="BZ6" s="13">
         <f>BP7*BP$4</f>
-        <v>0</v>
+        <v>5.2114642358544825E-3</v>
       </c>
       <c r="CA6" s="13">
-        <f t="shared" ref="CA6:CG21" si="16">BQ7*BQ$4</f>
-        <v>0.10365349727877445</v>
+        <f t="shared" ref="CA6:CG21" si="13">BQ7*BQ$4</f>
+        <v>4.764966740576497E-2</v>
       </c>
       <c r="CB6" s="13">
-        <f t="shared" si="16"/>
-        <v>5.6440233823825748E-4</v>
+        <f t="shared" si="13"/>
+        <v>6.2412745339574503E-4</v>
       </c>
       <c r="CC6" s="13">
-        <f t="shared" si="16"/>
-        <v>0.11755694416448295</v>
+        <f t="shared" si="13"/>
+        <v>6.9534368070953437E-2</v>
       </c>
       <c r="CD6" s="13">
-        <f t="shared" si="16"/>
-        <v>4.4155844155844164E-2</v>
+        <f t="shared" si="13"/>
+        <v>4.8531289910600267E-2</v>
       </c>
       <c r="CE6" s="13">
-        <f t="shared" si="16"/>
-        <v>0.25283189033189035</v>
+        <f t="shared" si="13"/>
+        <v>0.24597701149425291</v>
       </c>
       <c r="CF6" s="13">
-        <f t="shared" si="16"/>
-        <v>4.9242424242424247E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.0664112388250327E-2</v>
       </c>
       <c r="CG6" s="13">
-        <f t="shared" si="16"/>
-        <v>0.24454365079365081</v>
-      </c>
-      <c r="CI6" s="141" t="s">
+        <f t="shared" si="13"/>
+        <v>0.22916666666666671</v>
+      </c>
+      <c r="CI6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="CJ6" s="145">
+      <c r="CJ6" s="14">
         <f t="shared" si="4"/>
-        <v>6.9100183310751573E-3</v>
-      </c>
-      <c r="CK6" s="146">
+        <v>1.1590209335788838E-2</v>
+      </c>
+      <c r="CK6" s="14">
+        <f t="shared" si="4"/>
+        <v>0.11991786531895522</v>
+      </c>
+      <c r="CL6" s="14">
+        <f t="shared" si="4"/>
+        <v>0.12987434855650828</v>
+      </c>
+      <c r="CM6" s="14">
+        <f t="shared" si="4"/>
+        <v>0.33415125400519208</v>
+      </c>
+      <c r="CO6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CP6" s="14">
         <f t="shared" si="5"/>
-        <v>0.17127870203705065</v>
-      </c>
-      <c r="CL6" s="146">
+        <v>-0.32256104466940322</v>
+      </c>
+      <c r="CQ6" s="14">
         <f t="shared" si="6"/>
-        <v>9.6684000625181774E-2</v>
-      </c>
-      <c r="CM6" s="147">
+        <v>-9.9564832375530626E-3</v>
+      </c>
+      <c r="CR6" s="49">
         <f t="shared" si="7"/>
-        <v>0.38184643489397607</v>
-      </c>
-      <c r="CO6" s="141" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP6" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.37493641656290089</v>
-      </c>
-      <c r="CQ6" s="146">
-        <f t="shared" si="9"/>
-        <v>7.4594701411868872E-2</v>
-      </c>
-      <c r="CR6" s="49">
+        <v>0</v>
+      </c>
+      <c r="CS6" s="49">
+        <f t="shared" si="7"/>
+        <v>0.43798342964748282</v>
+      </c>
+      <c r="CU6" s="14"/>
+      <c r="CW6" s="107">
         <f t="shared" si="10"/>
-        <v>1.3255512805040576E-2</v>
-      </c>
-      <c r="CS6" s="153">
-        <f t="shared" si="10"/>
-        <v>0.54523536145147133</v>
-      </c>
-      <c r="CU6" s="14"/>
-      <c r="CW6" s="157">
-        <f t="shared" si="13"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CY6" s="14"/>
     </row>
@@ -7159,27 +7065,27 @@
       <c r="R7" s="23">
         <v>0</v>
       </c>
-      <c r="T7" s="107" t="s">
+      <c r="T7" s="112" t="s">
         <v>107</v>
       </c>
-      <c r="U7" s="108">
+      <c r="U7" s="113">
         <v>5</v>
       </c>
-      <c r="V7" s="108">
+      <c r="V7" s="113">
         <v>33</v>
       </c>
-      <c r="W7" s="108">
-        <v>1</v>
-      </c>
-      <c r="X7" s="108">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="109"/>
-      <c r="Z7" s="109"/>
-      <c r="AA7" s="109"/>
-      <c r="AB7" s="109"/>
-      <c r="AC7" s="109"/>
-      <c r="AD7" s="110"/>
+      <c r="W7" s="113">
+        <v>1</v>
+      </c>
+      <c r="X7" s="113">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="114"/>
+      <c r="Z7" s="114"/>
+      <c r="AA7" s="114"/>
+      <c r="AB7" s="114"/>
+      <c r="AC7" s="114"/>
+      <c r="AD7" s="123"/>
       <c r="AL7" s="39" t="s">
         <v>5</v>
       </c>
@@ -7195,7 +7101,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="80">
+      <c r="AP7" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -7237,35 +7143,35 @@
         <v>4</v>
       </c>
       <c r="BE7" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.74919614147909963</v>
       </c>
       <c r="BF7" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>4.519774011299435E-2</v>
       </c>
       <c r="BG7" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH7" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI7" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.95176848874598075</v>
       </c>
       <c r="BJ7" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.12994350282485875</v>
       </c>
       <c r="BK7" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BL7" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM7" s="45"/>
@@ -7273,16 +7179,16 @@
       <c r="BO7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="BP7" s="132">
+      <c r="BP7" s="13">
         <v>0.370288248337029</v>
       </c>
-      <c r="BQ7" s="132">
+      <c r="BQ7" s="13">
         <v>0.68070953436807091</v>
       </c>
-      <c r="BR7" s="132">
+      <c r="BR7" s="13">
         <v>8.8691796008869041E-3</v>
       </c>
-      <c r="BS7" s="132">
+      <c r="BS7" s="13">
         <v>0.31929046563192903</v>
       </c>
       <c r="BT7" s="13">
@@ -7301,79 +7207,79 @@
         <v>2</v>
       </c>
       <c r="BZ7" s="13">
-        <f t="shared" ref="BZ7:BZ21" si="17">BP8*BP$4</f>
-        <v>0</v>
+        <f t="shared" ref="BZ7:BZ21" si="14">BP8*BP$4</f>
+        <v>1.3894213702520412E-2</v>
       </c>
       <c r="CA7" s="13">
-        <f t="shared" si="16"/>
-        <v>0.1512997386000581</v>
+        <f t="shared" si="13"/>
+        <v>6.955271565495208E-2</v>
       </c>
       <c r="CB7" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CC7" s="13">
-        <f t="shared" si="16"/>
-        <v>2.3525994772001331E-3</v>
+        <f t="shared" si="13"/>
+        <v>1.3915512957046606E-3</v>
       </c>
       <c r="CD7" s="13">
-        <f t="shared" si="16"/>
-        <v>2.5585284280936458E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.8120555107061858E-2</v>
       </c>
       <c r="CE7" s="13">
-        <f t="shared" si="16"/>
-        <v>0.28677409546974764</v>
+        <f t="shared" si="13"/>
+        <v>0.27899896205743285</v>
       </c>
       <c r="CF7" s="13">
-        <f t="shared" si="16"/>
-        <v>1.9565217391304339E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.410333294891015E-2</v>
       </c>
       <c r="CG7" s="13">
-        <f t="shared" si="16"/>
-        <v>0.22031772575250835</v>
-      </c>
-      <c r="CI7" s="141" t="s">
+        <f t="shared" si="13"/>
+        <v>0.20646407565448047</v>
+      </c>
+      <c r="CI7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="CJ7" s="145">
+      <c r="CJ7" s="14">
         <f t="shared" si="4"/>
-        <v>1.658404399458038E-2</v>
-      </c>
-      <c r="CK7" s="146">
+        <v>2.3321147845900073E-2</v>
+      </c>
+      <c r="CK7" s="14">
+        <f t="shared" si="4"/>
+        <v>0.1894816350523244</v>
+      </c>
+      <c r="CL7" s="14">
+        <f t="shared" si="4"/>
+        <v>8.5255419230731197E-2</v>
+      </c>
+      <c r="CM7" s="14">
+        <f t="shared" si="4"/>
+        <v>0.27768159340290666</v>
+      </c>
+      <c r="CO7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP7" s="14">
         <f t="shared" si="5"/>
-        <v>0.24808867230641363</v>
-      </c>
-      <c r="CL7" s="146">
+        <v>-0.2543604455570066</v>
+      </c>
+      <c r="CQ7" s="14">
         <f t="shared" si="6"/>
-        <v>5.980484805701989E-2</v>
-      </c>
-      <c r="CM7" s="147">
+        <v>0.10422621582159321</v>
+      </c>
+      <c r="CR7" s="49">
         <f t="shared" si="7"/>
-        <v>0.31358894366705004</v>
-      </c>
-      <c r="CO7" s="141" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP7" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.29700489967246968</v>
-      </c>
-      <c r="CQ7" s="146">
-        <f t="shared" si="9"/>
-        <v>0.18828382424939374</v>
-      </c>
-      <c r="CR7" s="49">
+        <v>9.5554371204441171E-2</v>
+      </c>
+      <c r="CS7" s="49">
+        <f t="shared" si="7"/>
+        <v>0.5979623177074187</v>
+      </c>
+      <c r="CU7" s="14"/>
+      <c r="CW7" s="107">
         <f t="shared" si="10"/>
-        <v>0.10548048879098604</v>
-      </c>
-      <c r="CS7" s="153">
-        <f t="shared" si="10"/>
-        <v>0.67977626405311609</v>
-      </c>
-      <c r="CU7" s="14"/>
-      <c r="CW7" s="157">
-        <f t="shared" si="13"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY7" s="14"/>
     </row>
@@ -7429,25 +7335,25 @@
       <c r="R8" s="23">
         <v>2</v>
       </c>
-      <c r="T8" s="107"/>
-      <c r="U8" s="108">
+      <c r="T8" s="112"/>
+      <c r="U8" s="113">
         <v>9</v>
       </c>
-      <c r="V8" s="108">
+      <c r="V8" s="113">
         <v>38</v>
       </c>
-      <c r="W8" s="108">
-        <v>1</v>
-      </c>
-      <c r="X8" s="108">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="109"/>
-      <c r="Z8" s="109"/>
-      <c r="AA8" s="109"/>
-      <c r="AB8" s="109"/>
-      <c r="AC8" s="109"/>
-      <c r="AD8" s="110"/>
+      <c r="W8" s="113">
+        <v>1</v>
+      </c>
+      <c r="X8" s="113">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="114"/>
+      <c r="Z8" s="114"/>
+      <c r="AA8" s="114"/>
+      <c r="AB8" s="114"/>
+      <c r="AC8" s="114"/>
+      <c r="AD8" s="123"/>
       <c r="AL8" s="39" t="s">
         <v>6</v>
       </c>
@@ -7463,7 +7369,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP8" s="80">
+      <c r="AP8" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7505,35 +7411,35 @@
         <v>5</v>
       </c>
       <c r="BE8" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.89067524115755625</v>
       </c>
       <c r="BF8" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.13559322033898305</v>
       </c>
       <c r="BG8" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH8" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI8" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.98392282958199362</v>
       </c>
       <c r="BJ8" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.49152542372881358</v>
       </c>
       <c r="BK8" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BL8" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM8" s="45"/>
@@ -7569,78 +7475,78 @@
         <v>4</v>
       </c>
       <c r="BZ8" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>8.7680728857199436E-3</v>
       </c>
       <c r="CA8" s="13">
-        <f t="shared" si="16"/>
-        <v>0.12051531356344192</v>
+        <f t="shared" si="13"/>
+        <v>5.5401069518716588E-2</v>
       </c>
       <c r="CB8" s="13">
-        <f t="shared" si="16"/>
-        <v>2.5522605736509455E-3</v>
+        <f t="shared" si="13"/>
+        <v>2.8223410576351726E-3</v>
       </c>
       <c r="CC8" s="13">
-        <f t="shared" si="16"/>
-        <v>7.6786582401555684E-2</v>
+        <f t="shared" si="13"/>
+        <v>4.5418894830659549E-2</v>
       </c>
       <c r="CD8" s="13">
-        <f t="shared" si="16"/>
-        <v>1.4488636363636363E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.5924329501915708E-2</v>
       </c>
       <c r="CE8" s="13">
-        <f t="shared" si="16"/>
-        <v>7.1330492424242414E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.9396551724137931E-2</v>
       </c>
       <c r="CF8" s="13">
-        <f t="shared" si="16"/>
-        <v>0.14218749999999997</v>
+        <f t="shared" si="13"/>
+        <v>0.17516762452107276</v>
       </c>
       <c r="CG8" s="13">
-        <f t="shared" si="16"/>
-        <v>0.37408854166666661</v>
-      </c>
-      <c r="CI8" s="141" t="s">
+        <f t="shared" si="13"/>
+        <v>0.35056573275862069</v>
+      </c>
+      <c r="CI8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="CJ8" s="145">
+      <c r="CJ8" s="14">
         <f t="shared" si="4"/>
-        <v>4.6976261958897203E-2</v>
-      </c>
-      <c r="CK8" s="146">
+        <v>5.5636303457809101E-2</v>
+      </c>
+      <c r="CK8" s="14">
+        <f t="shared" si="4"/>
+        <v>0.24362662788892309</v>
+      </c>
+      <c r="CL8" s="14">
+        <f t="shared" si="4"/>
+        <v>6.8963163637445909E-2</v>
+      </c>
+      <c r="CM8" s="14">
+        <f t="shared" si="4"/>
+        <v>0.25025924333138244</v>
+      </c>
+      <c r="CO8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP8" s="14">
         <f t="shared" si="5"/>
-        <v>0.30164920936202477</v>
-      </c>
-      <c r="CL8" s="146">
+        <v>-0.19462293987357335</v>
+      </c>
+      <c r="CQ8" s="14">
         <f t="shared" si="6"/>
-        <v>4.7289134200185552E-2</v>
-      </c>
-      <c r="CM8" s="147">
+        <v>0.17466346425147716</v>
+      </c>
+      <c r="CR8" s="49">
         <f t="shared" si="7"/>
-        <v>0.28777897380035861</v>
-      </c>
-      <c r="CO8" s="141" t="s">
-        <v>6</v>
-      </c>
-      <c r="CP8" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.2408027118414614</v>
-      </c>
-      <c r="CQ8" s="146">
-        <f t="shared" si="9"/>
-        <v>0.25436007516183923</v>
-      </c>
-      <c r="CR8" s="49">
+        <v>0.1792512868795505</v>
+      </c>
+      <c r="CS8" s="49">
+        <f t="shared" si="7"/>
+        <v>0.69665040946444801</v>
+      </c>
+      <c r="CU8" s="14"/>
+      <c r="CW8" s="107">
         <f t="shared" si="10"/>
-        <v>0.17199074843805262</v>
-      </c>
-      <c r="CS8" s="153">
-        <f t="shared" si="10"/>
-        <v>0.75797159370657774</v>
-      </c>
-      <c r="CU8" s="14"/>
-      <c r="CW8" s="157">
-        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="CY8" s="14"/>
@@ -7697,25 +7603,25 @@
       <c r="R9" s="23">
         <v>2</v>
       </c>
-      <c r="T9" s="107"/>
-      <c r="U9" s="108">
+      <c r="T9" s="112"/>
+      <c r="U9" s="113">
         <v>10</v>
       </c>
-      <c r="V9" s="108">
+      <c r="V9" s="113">
         <v>40</v>
       </c>
-      <c r="W9" s="108">
-        <v>1</v>
-      </c>
-      <c r="X9" s="108">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="109"/>
-      <c r="Z9" s="109"/>
-      <c r="AA9" s="109"/>
-      <c r="AB9" s="109"/>
-      <c r="AC9" s="109"/>
-      <c r="AD9" s="110"/>
+      <c r="W9" s="113">
+        <v>1</v>
+      </c>
+      <c r="X9" s="113">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="114"/>
+      <c r="Z9" s="114"/>
+      <c r="AA9" s="114"/>
+      <c r="AB9" s="114"/>
+      <c r="AC9" s="114"/>
+      <c r="AD9" s="123"/>
       <c r="AL9" s="39" t="s">
         <v>8</v>
       </c>
@@ -7731,7 +7637,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP9" s="80">
+      <c r="AP9" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7773,35 +7679,35 @@
         <v>6</v>
       </c>
       <c r="BE9" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.81672025723472674</v>
       </c>
       <c r="BF9" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="BG9" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH9" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI9" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BJ9" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.68926553672316382</v>
       </c>
       <c r="BK9" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL9" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM9" s="45"/>
@@ -7837,78 +7743,78 @@
         <v>5</v>
       </c>
       <c r="BZ9" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.1466230936819172E-2</v>
       </c>
       <c r="CA9" s="13">
-        <f t="shared" si="16"/>
-        <v>0.13704545454545458</v>
+        <f t="shared" si="13"/>
+        <v>6.3000000000000014E-2</v>
       </c>
       <c r="CB9" s="13">
-        <f t="shared" si="16"/>
-        <v>9.3582887700534463E-4</v>
+        <f t="shared" si="13"/>
+        <v>1.034858387799561E-3</v>
       </c>
       <c r="CC9" s="13">
-        <f t="shared" si="16"/>
-        <v>3.6818181818181826E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.1777777777777785E-2</v>
       </c>
       <c r="CD9" s="13">
-        <f t="shared" si="16"/>
-        <v>3.4772727272727275E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.8218390804597706E-2</v>
       </c>
       <c r="CE9" s="13">
-        <f t="shared" si="16"/>
-        <v>0.21585227272727275</v>
+        <f t="shared" si="13"/>
+        <v>0.21000000000000005</v>
       </c>
       <c r="CF9" s="13">
-        <f t="shared" si="16"/>
-        <v>6.6477272727272718E-2</v>
+        <f t="shared" si="13"/>
+        <v>8.1896551724137928E-2</v>
       </c>
       <c r="CG9" s="13">
-        <f t="shared" si="16"/>
-        <v>0.2709375</v>
-      </c>
-      <c r="CI9" s="141" t="s">
+        <f t="shared" si="13"/>
+        <v>0.25390086206896556</v>
+      </c>
+      <c r="CI9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="CJ9" s="145">
+      <c r="CJ9" s="14">
         <f t="shared" si="4"/>
-        <v>2.6566672418502545E-2</v>
-      </c>
-      <c r="CK9" s="146">
+        <v>3.4057360841112813E-2</v>
+      </c>
+      <c r="CK9" s="14">
+        <f t="shared" si="4"/>
+        <v>0.16955302572318193</v>
+      </c>
+      <c r="CL9" s="14">
+        <f t="shared" si="4"/>
+        <v>0.10452906598941999</v>
+      </c>
+      <c r="CM9" s="14">
+        <f t="shared" si="4"/>
+        <v>0.30442190994920881</v>
+      </c>
+      <c r="CO9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CP9" s="14">
         <f t="shared" si="5"/>
-        <v>0.22540109794571997</v>
-      </c>
-      <c r="CL9" s="146">
+        <v>-0.27036454910809599</v>
+      </c>
+      <c r="CQ9" s="14">
         <f t="shared" si="6"/>
-        <v>7.5747082304677818E-2</v>
-      </c>
-      <c r="CM9" s="147">
+        <v>6.5023959733761932E-2</v>
+      </c>
+      <c r="CR9" s="49">
         <f t="shared" si="7"/>
-        <v>0.34335918718883396</v>
-      </c>
-      <c r="CO9" s="141" t="s">
-        <v>8</v>
-      </c>
-      <c r="CP9" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.31679251477033143</v>
-      </c>
-      <c r="CQ9" s="146">
-        <f t="shared" si="9"/>
-        <v>0.14965401564104214</v>
-      </c>
-      <c r="CR9" s="49">
+        <v>7.3131370946117324E-2</v>
+      </c>
+      <c r="CS9" s="49">
+        <f t="shared" si="7"/>
+        <v>0.54303689213901918</v>
+      </c>
+      <c r="CU9" s="14"/>
+      <c r="CW9" s="107">
         <f t="shared" si="10"/>
-        <v>8.2063617157585256E-2</v>
-      </c>
-      <c r="CS9" s="153">
-        <f t="shared" si="10"/>
-        <v>0.6340613426272208</v>
-      </c>
-      <c r="CU9" s="14"/>
-      <c r="CW9" s="157">
-        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="CY9" s="14"/>
@@ -7965,25 +7871,25 @@
       <c r="R10" s="23">
         <v>2</v>
       </c>
-      <c r="T10" s="107"/>
-      <c r="U10" s="108">
+      <c r="T10" s="112"/>
+      <c r="U10" s="113">
         <v>12</v>
       </c>
-      <c r="V10" s="108">
+      <c r="V10" s="113">
         <v>52</v>
       </c>
-      <c r="W10" s="108">
-        <v>1</v>
-      </c>
-      <c r="X10" s="108">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="109"/>
-      <c r="Z10" s="109"/>
-      <c r="AA10" s="109"/>
-      <c r="AB10" s="109"/>
-      <c r="AC10" s="109"/>
-      <c r="AD10" s="110"/>
+      <c r="W10" s="113">
+        <v>1</v>
+      </c>
+      <c r="X10" s="113">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="114"/>
+      <c r="Z10" s="114"/>
+      <c r="AA10" s="114"/>
+      <c r="AB10" s="114"/>
+      <c r="AC10" s="114"/>
+      <c r="AD10" s="123"/>
       <c r="AL10" s="39" t="s">
         <v>9</v>
       </c>
@@ -7999,7 +7905,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP10" s="80">
+      <c r="AP10" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -8041,35 +7947,35 @@
         <v>8</v>
       </c>
       <c r="BE10" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BF10" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.1864406779661017</v>
       </c>
       <c r="BG10" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH10" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BI10" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="BJ10" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.35028248587570621</v>
       </c>
       <c r="BK10" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BL10" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM10" s="45"/>
@@ -8105,79 +8011,79 @@
         <v>6</v>
       </c>
       <c r="BZ10" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.0272456364410388E-2</v>
       </c>
       <c r="CA10" s="13">
-        <f t="shared" si="16"/>
-        <v>0.12733150470219437</v>
+        <f t="shared" si="13"/>
+        <v>5.85344827586207E-2</v>
       </c>
       <c r="CB10" s="13">
-        <f t="shared" si="16"/>
-        <v>3.6572622779519346E-3</v>
+        <f t="shared" si="13"/>
+        <v>4.0442741592166889E-3</v>
       </c>
       <c r="CC10" s="13">
-        <f t="shared" si="16"/>
-        <v>6.0305642633228823E-2</v>
+        <f t="shared" si="13"/>
+        <v>3.567049808429118E-2</v>
       </c>
       <c r="CD10" s="13">
-        <f t="shared" si="16"/>
-        <v>9.84978540772532E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.10825810270830248</v>
       </c>
       <c r="CE10" s="13">
-        <f t="shared" si="16"/>
-        <v>0.31178306671868899</v>
+        <f t="shared" si="13"/>
+        <v>0.3033298801243155</v>
       </c>
       <c r="CF10" s="13">
-        <f t="shared" si="16"/>
-        <v>4.1845493562231752E-2</v>
+        <f t="shared" si="13"/>
+        <v>5.1551477480144041E-2</v>
       </c>
       <c r="CG10" s="13">
-        <f t="shared" si="16"/>
-        <v>0.20246781115879825</v>
-      </c>
-      <c r="CI10" s="141" t="s">
+        <f t="shared" si="13"/>
+        <v>0.18973656948349857</v>
+      </c>
+      <c r="CI10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="CJ10" s="145">
+      <c r="CJ10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2601857138738888E-2</v>
-      </c>
-      <c r="CK10" s="146">
+        <v>1.6796628814205249E-2</v>
+      </c>
+      <c r="CK10" s="14">
+        <f t="shared" si="4"/>
+        <v>0.2304882572731457</v>
+      </c>
+      <c r="CL10" s="14">
+        <f t="shared" si="4"/>
+        <v>4.4490558411266604E-2</v>
+      </c>
+      <c r="CM10" s="14">
+        <f t="shared" si="4"/>
+        <v>0.32530086575799905</v>
+      </c>
+      <c r="CO10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="CP10" s="14">
         <f t="shared" si="5"/>
-        <v>0.27669890116542795</v>
-      </c>
-      <c r="CL10" s="146">
+        <v>-0.30850423694379381</v>
+      </c>
+      <c r="CQ10" s="14">
         <f t="shared" si="6"/>
-        <v>2.7079047308089556E-2</v>
-      </c>
-      <c r="CM10" s="147">
+        <v>0.18599769886187911</v>
+      </c>
+      <c r="CR10" s="49">
         <f t="shared" si="7"/>
-        <v>0.37696442947608028</v>
-      </c>
-      <c r="CO10" s="141" t="s">
-        <v>9</v>
-      </c>
-      <c r="CP10" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.36436257233734137</v>
-      </c>
-      <c r="CQ10" s="146">
-        <f t="shared" si="9"/>
-        <v>0.2496198538573384</v>
-      </c>
-      <c r="CR10" s="49">
+        <v>1.9694686569376348E-2</v>
+      </c>
+      <c r="CS10" s="49">
+        <f t="shared" si="7"/>
+        <v>0.71253055825164124</v>
+      </c>
+      <c r="CU10" s="14"/>
+      <c r="CW10" s="107">
         <f t="shared" si="10"/>
-        <v>2.5768711170631359E-2</v>
-      </c>
-      <c r="CS10" s="153">
-        <f t="shared" si="10"/>
-        <v>0.75236196600498573</v>
-      </c>
-      <c r="CU10" s="14"/>
-      <c r="CW10" s="157">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CY10" s="14"/>
     </row>
@@ -8233,25 +8139,25 @@
       <c r="R11" s="23">
         <v>2</v>
       </c>
-      <c r="T11" s="107"/>
-      <c r="U11" s="108">
+      <c r="T11" s="112"/>
+      <c r="U11" s="113">
         <v>20</v>
       </c>
-      <c r="V11" s="108">
+      <c r="V11" s="113">
         <v>54</v>
       </c>
-      <c r="W11" s="108">
-        <v>1</v>
-      </c>
-      <c r="X11" s="108">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="109"/>
-      <c r="Z11" s="109"/>
-      <c r="AA11" s="109"/>
-      <c r="AB11" s="109"/>
-      <c r="AC11" s="109"/>
-      <c r="AD11" s="110"/>
+      <c r="W11" s="113">
+        <v>1</v>
+      </c>
+      <c r="X11" s="113">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="114"/>
+      <c r="Z11" s="114"/>
+      <c r="AA11" s="114"/>
+      <c r="AB11" s="114"/>
+      <c r="AC11" s="114"/>
+      <c r="AD11" s="123"/>
       <c r="AL11" s="39" t="s">
         <v>10</v>
       </c>
@@ -8267,7 +8173,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP11" s="80">
+      <c r="AP11" s="79">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8309,35 +8215,35 @@
         <v>9</v>
       </c>
       <c r="BE11" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.62700964630225076</v>
       </c>
       <c r="BF11" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.14124293785310735</v>
       </c>
       <c r="BG11" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH11" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BI11" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BJ11" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BK11" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL11" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM11" s="45"/>
@@ -8373,79 +8279,79 @@
         <v>8</v>
       </c>
       <c r="BZ11" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.133398885611275E-2</v>
       </c>
       <c r="CA11" s="13">
-        <f t="shared" si="16"/>
-        <v>0.13520380799141862</v>
+        <f t="shared" si="13"/>
+        <v>6.2153392330383486E-2</v>
       </c>
       <c r="CB11" s="13">
-        <f t="shared" si="16"/>
-        <v>1.8771788683293112E-3</v>
+        <f t="shared" si="13"/>
+        <v>2.0758221348191855E-3</v>
       </c>
       <c r="CC11" s="13">
-        <f t="shared" si="16"/>
-        <v>4.1271118262268702E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.4411668305473616E-2</v>
       </c>
       <c r="CD11" s="13">
-        <f t="shared" si="16"/>
-        <v>5.5703883495145622E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.1223635754938062E-2</v>
       </c>
       <c r="CE11" s="13">
-        <f t="shared" si="16"/>
-        <v>0.17921447484554279</v>
+        <f t="shared" si="13"/>
+        <v>0.1743555406762638</v>
       </c>
       <c r="CF11" s="13">
-        <f t="shared" si="16"/>
-        <v>9.8962930273609861E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.1219171967414351</v>
       </c>
       <c r="CG11" s="13">
-        <f t="shared" si="16"/>
-        <v>0.29708737864077667</v>
-      </c>
-      <c r="CI11" s="141" t="s">
+        <f t="shared" si="13"/>
+        <v>0.27840642785403413</v>
+      </c>
+      <c r="CI11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="CJ11" s="145">
+      <c r="CJ11" s="14">
         <f t="shared" si="4"/>
-        <v>2.9995572486338645E-2</v>
-      </c>
-      <c r="CK11" s="146">
+        <v>3.5140252957498341E-2</v>
+      </c>
+      <c r="CK11" s="14">
+        <f t="shared" si="4"/>
+        <v>0.22147706372733211</v>
+      </c>
+      <c r="CL11" s="14">
+        <f t="shared" si="4"/>
+        <v>0.10257751268604759</v>
+      </c>
+      <c r="CM11" s="14">
+        <f t="shared" si="4"/>
+        <v>0.35314387839961392</v>
+      </c>
+      <c r="CO11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP11" s="14">
         <f t="shared" si="5"/>
-        <v>0.26309407464776463</v>
-      </c>
-      <c r="CL11" s="146">
+        <v>-0.31800362544211558</v>
+      </c>
+      <c r="CQ11" s="14">
         <f t="shared" si="6"/>
-        <v>7.7858392522428155E-2</v>
-      </c>
-      <c r="CM11" s="147">
+        <v>0.11889955104128452</v>
+      </c>
+      <c r="CR11" s="49">
         <f t="shared" si="7"/>
-        <v>0.409909400041085</v>
-      </c>
-      <c r="CO11" s="141" t="s">
-        <v>10</v>
-      </c>
-      <c r="CP11" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.37991382755474634</v>
-      </c>
-      <c r="CQ11" s="146">
-        <f t="shared" si="9"/>
-        <v>0.18523568212533648</v>
-      </c>
-      <c r="CR11" s="49">
+        <v>6.3853006314624075E-3</v>
+      </c>
+      <c r="CS11" s="49">
+        <f t="shared" si="7"/>
+        <v>0.61852080749544647</v>
+      </c>
+      <c r="CU11" s="14"/>
+      <c r="CW11" s="107">
         <f t="shared" si="10"/>
-        <v>7.3651923350756014E-3</v>
-      </c>
-      <c r="CS11" s="153">
-        <f t="shared" si="10"/>
-        <v>0.67616906063388638</v>
-      </c>
-      <c r="CU11" s="14"/>
-      <c r="CW11" s="157">
-        <f t="shared" si="13"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CY11" s="14"/>
     </row>
@@ -8501,25 +8407,25 @@
       <c r="R12" s="23">
         <v>0</v>
       </c>
-      <c r="T12" s="107"/>
-      <c r="U12" s="108">
+      <c r="T12" s="112"/>
+      <c r="U12" s="113">
         <v>20</v>
       </c>
-      <c r="V12" s="108">
+      <c r="V12" s="113">
         <v>56</v>
       </c>
-      <c r="W12" s="108">
+      <c r="W12" s="113">
         <v>2</v>
       </c>
-      <c r="X12" s="108">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="109"/>
-      <c r="Z12" s="109"/>
-      <c r="AA12" s="109"/>
-      <c r="AB12" s="109"/>
-      <c r="AC12" s="109"/>
-      <c r="AD12" s="110"/>
+      <c r="X12" s="113">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="114"/>
+      <c r="Z12" s="114"/>
+      <c r="AA12" s="114"/>
+      <c r="AB12" s="114"/>
+      <c r="AC12" s="114"/>
+      <c r="AD12" s="123"/>
       <c r="AL12" s="39" t="s">
         <v>11</v>
       </c>
@@ -8535,7 +8441,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="80">
+      <c r="AP12" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8577,35 +8483,35 @@
         <v>10</v>
       </c>
       <c r="BE12" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.54019292604501612</v>
       </c>
       <c r="BF12" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.16949152542372881</v>
       </c>
       <c r="BG12" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH12" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="BI12" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BJ12" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="BK12" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.34615384615384615</v>
       </c>
       <c r="BL12" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BM12" s="45"/>
@@ -8641,79 +8547,79 @@
         <v>9</v>
       </c>
       <c r="BZ12" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>6.7431067431067424E-3</v>
       </c>
       <c r="CA12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.10887312932767479</v>
+        <f t="shared" si="13"/>
+        <v>5.0049140049140052E-2</v>
       </c>
       <c r="CB12" s="13">
-        <f t="shared" si="16"/>
-        <v>3.1270940361849461E-3</v>
+        <f t="shared" si="13"/>
+        <v>3.4580034580034588E-3</v>
       </c>
       <c r="CC12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.10493634129997767</v>
+        <f t="shared" si="13"/>
+        <v>6.206934206934208E-2</v>
       </c>
       <c r="CD12" s="13">
-        <f t="shared" si="16"/>
-        <v>2.6423045040066314E-2</v>
+        <f t="shared" si="13"/>
+        <v>2.904133039863047E-2</v>
       </c>
       <c r="CE12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.32035092567007456</v>
+        <f t="shared" si="13"/>
+        <v>0.31166544387380779</v>
       </c>
       <c r="CF12" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CG12" s="13">
-        <f t="shared" si="16"/>
-        <v>0.19635258358662611</v>
-      </c>
-      <c r="CI12" s="141" t="s">
-        <v>11</v>
-      </c>
-      <c r="CJ12" s="145">
-        <f t="shared" si="4"/>
-        <v>4.9082820791134747E-2</v>
-      </c>
-      <c r="CK12" s="146">
+        <f t="shared" si="13"/>
+        <v>0.18400586940572267</v>
+      </c>
+      <c r="CI12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ12" s="14">
+        <f>(BZ21+CD21+BZ38+CD38)/$T$41</f>
+        <v>6.4383649218111181E-3</v>
+      </c>
+      <c r="CK12" s="14">
+        <f t="shared" ref="CK12:CM12" si="15">(CA21+CE21+CA38+CE38)/$T$41</f>
+        <v>0.25639003048119946</v>
+      </c>
+      <c r="CL12" s="14">
+        <f t="shared" si="15"/>
+        <v>5.9029608857698715E-2</v>
+      </c>
+      <c r="CM12" s="14">
+        <f t="shared" si="15"/>
+        <v>0.234405793536756</v>
+      </c>
+      <c r="CO12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="CP12" s="14">
         <f t="shared" si="5"/>
-        <v>0.27815016911219825</v>
-      </c>
-      <c r="CL12" s="146">
+        <v>-0.22796742861494487</v>
+      </c>
+      <c r="CQ12" s="14">
         <f t="shared" si="6"/>
-        <v>5.6906176274963978E-2</v>
-      </c>
-      <c r="CM12" s="147">
+        <v>0.19736042162350076</v>
+      </c>
+      <c r="CR12" s="49">
         <f t="shared" si="7"/>
-        <v>0.23863452931985304</v>
-      </c>
-      <c r="CO12" s="141" t="s">
-        <v>11</v>
-      </c>
-      <c r="CP12" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.1895517085287183</v>
-      </c>
-      <c r="CQ12" s="146">
-        <f t="shared" si="9"/>
-        <v>0.22124399283723428</v>
-      </c>
-      <c r="CR12" s="49">
+        <v>0.13253305131736207</v>
+      </c>
+      <c r="CS12" s="49">
+        <f t="shared" si="7"/>
+        <v>0.72845062116586545</v>
+      </c>
+      <c r="CU12" s="14"/>
+      <c r="CW12" s="107">
         <f t="shared" si="10"/>
-        <v>0.23264172429957472</v>
-      </c>
-      <c r="CS12" s="153">
-        <f t="shared" si="10"/>
-        <v>0.71878167390263936</v>
-      </c>
-      <c r="CU12" s="14"/>
-      <c r="CW12" s="157">
-        <f t="shared" si="13"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CY12" s="14"/>
     </row>
@@ -8769,25 +8675,25 @@
       <c r="R13" s="23">
         <v>7</v>
       </c>
-      <c r="T13" s="107"/>
-      <c r="U13" s="108">
+      <c r="T13" s="112"/>
+      <c r="U13" s="113">
         <v>28</v>
       </c>
-      <c r="V13" s="108">
+      <c r="V13" s="113">
         <v>60</v>
       </c>
-      <c r="W13" s="108">
+      <c r="W13" s="113">
         <v>2</v>
       </c>
-      <c r="X13" s="108">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="109"/>
-      <c r="Z13" s="109"/>
-      <c r="AA13" s="109"/>
-      <c r="AB13" s="109"/>
-      <c r="AC13" s="109"/>
-      <c r="AD13" s="110"/>
+      <c r="X13" s="113">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="114"/>
+      <c r="Z13" s="114"/>
+      <c r="AA13" s="114"/>
+      <c r="AB13" s="114"/>
+      <c r="AC13" s="114"/>
+      <c r="AD13" s="123"/>
       <c r="AL13" s="39" t="s">
         <v>12</v>
       </c>
@@ -8803,7 +8709,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP13" s="80">
+      <c r="AP13" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8845,35 +8751,35 @@
         <v>11</v>
       </c>
       <c r="BE13" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="BF13" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="BG13" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH13" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="BI13" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BJ13" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="BK13" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BL13" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM13" s="45"/>
@@ -8909,79 +8815,79 @@
         <v>10</v>
       </c>
       <c r="BZ13" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>5.6837606837606847E-3</v>
       </c>
       <c r="CA13" s="13">
+        <f t="shared" si="13"/>
+        <v>4.5937500000000006E-2</v>
+      </c>
+      <c r="CB13" s="13">
+        <f t="shared" si="13"/>
+        <v>6.4280626780626781E-3</v>
+      </c>
+      <c r="CC13" s="13">
+        <f t="shared" si="13"/>
+        <v>7.4861111111111114E-2</v>
+      </c>
+      <c r="CD13" s="13">
+        <f t="shared" si="13"/>
+        <v>5.6480380499405465E-2</v>
+      </c>
+      <c r="CE13" s="13">
+        <f t="shared" si="13"/>
+        <v>0.15980975029726521</v>
+      </c>
+      <c r="CF13" s="13">
+        <f t="shared" si="13"/>
+        <v>0.13017382934148689</v>
+      </c>
+      <c r="CG13" s="13">
+        <f t="shared" si="13"/>
+        <v>0.28840665873959576</v>
+      </c>
+      <c r="CI13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ13" s="14">
+        <f>(BZ14+CD14+BZ31+CD31)/$T$41</f>
+        <v>5.957316933234523E-2</v>
+      </c>
+      <c r="CK13" s="14">
+        <f t="shared" ref="CK13:CM19" si="16">(CA14+CE14+CA31+CE31)/$T$41</f>
+        <v>0.21018308004035699</v>
+      </c>
+      <c r="CL13" s="14">
         <f t="shared" si="16"/>
-        <v>9.9928977272727273E-2</v>
-      </c>
-      <c r="CB13" s="13">
+        <v>8.3929560172251547E-2</v>
+      </c>
+      <c r="CM13" s="14">
         <f t="shared" si="16"/>
-        <v>5.8129370629370625E-3</v>
-      </c>
-      <c r="CC13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.12656249999999999</v>
-      </c>
-      <c r="CD13" s="13">
-        <f t="shared" si="16"/>
-        <v>5.1388266905508281E-2</v>
-      </c>
-      <c r="CE13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.16426332288401257</v>
-      </c>
-      <c r="CF13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.10566502463054187</v>
-      </c>
-      <c r="CG13" s="13">
-        <f t="shared" si="16"/>
-        <v>0.30775862068965515</v>
-      </c>
-      <c r="CI13" s="141" t="s">
-        <v>12</v>
-      </c>
-      <c r="CJ13" s="145">
-        <f t="shared" si="4"/>
-        <v>2.0482574825292324E-2</v>
-      </c>
-      <c r="CK13" s="146">
+        <v>0.21350903151379916</v>
+      </c>
+      <c r="CO13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CP13" s="14">
         <f t="shared" si="5"/>
-        <v>0.31494820094522363</v>
-      </c>
-      <c r="CL13" s="146">
+        <v>-0.15393586218145394</v>
+      </c>
+      <c r="CQ13" s="14">
         <f t="shared" si="6"/>
-        <v>4.6341831210398934E-2</v>
-      </c>
-      <c r="CM13" s="147">
+        <v>0.12625351986810546</v>
+      </c>
+      <c r="CR13" s="49">
         <f t="shared" si="7"/>
-        <v>0.40662010268167592</v>
-      </c>
-      <c r="CO13" s="141" t="s">
-        <v>12</v>
-      </c>
-      <c r="CP13" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.38613752785638361</v>
-      </c>
-      <c r="CQ13" s="146">
-        <f t="shared" si="9"/>
-        <v>0.26860636973482471</v>
-      </c>
-      <c r="CR13" s="49">
+        <v>0.23625706359728077</v>
+      </c>
+      <c r="CS13" s="49">
+        <f t="shared" si="7"/>
+        <v>0.62882429274703289</v>
+      </c>
+      <c r="CU13" s="14"/>
+      <c r="CW13" s="107">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="CS13" s="153">
-        <f t="shared" si="10"/>
-        <v>0.77483080840311114</v>
-      </c>
-      <c r="CU13" s="14"/>
-      <c r="CW13" s="157">
-        <f t="shared" si="13"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="CY13" s="14"/>
     </row>
@@ -9037,25 +8943,25 @@
       <c r="R14" s="23">
         <v>1</v>
       </c>
-      <c r="T14" s="107"/>
-      <c r="U14" s="108">
+      <c r="T14" s="112"/>
+      <c r="U14" s="113">
         <v>28</v>
       </c>
-      <c r="V14" s="108">
+      <c r="V14" s="113">
         <v>63</v>
       </c>
-      <c r="W14" s="108">
+      <c r="W14" s="113">
         <v>2</v>
       </c>
-      <c r="X14" s="108">
+      <c r="X14" s="113">
         <v>2</v>
       </c>
-      <c r="Y14" s="109"/>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109"/>
-      <c r="AB14" s="109"/>
-      <c r="AC14" s="109"/>
-      <c r="AD14" s="110"/>
+      <c r="Y14" s="114"/>
+      <c r="Z14" s="114"/>
+      <c r="AA14" s="114"/>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="114"/>
+      <c r="AD14" s="123"/>
       <c r="AL14" s="39" t="s">
         <v>13</v>
       </c>
@@ -9071,7 +8977,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP14" s="80">
+      <c r="AP14" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9113,35 +9019,35 @@
         <v>12</v>
       </c>
       <c r="BE14" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BF14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="BG14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="BI14" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="BJ14" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="BK14" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.61538461538461542</v>
       </c>
       <c r="BL14" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM14" s="45"/>
@@ -9177,79 +9083,79 @@
         <v>11</v>
       </c>
       <c r="BZ14" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.3805142722340173E-2</v>
       </c>
       <c r="CA14" s="13">
+        <f t="shared" si="13"/>
+        <v>6.9331210191082807E-2</v>
+      </c>
+      <c r="CB14" s="13">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="CC14" s="13">
+        <f t="shared" si="13"/>
+        <v>2.0806794055201728E-3</v>
+      </c>
+      <c r="CD14" s="13">
+        <f t="shared" si="13"/>
+        <v>0.11311272614813668</v>
+      </c>
+      <c r="CE14" s="13">
+        <f t="shared" si="13"/>
+        <v>0.29095407453224065</v>
+      </c>
+      <c r="CF14" s="13">
+        <f t="shared" si="13"/>
+        <v>6.3656512550899422E-2</v>
+      </c>
+      <c r="CG14" s="13">
+        <f t="shared" si="13"/>
+        <v>0.19824493582805011</v>
+      </c>
+      <c r="CI14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="CJ14" s="14">
+        <f t="shared" ref="CJ14:CJ19" si="17">(BZ15+CD15+BZ32+CD32)/$T$41</f>
+        <v>2.2177676301761779E-2</v>
+      </c>
+      <c r="CK14" s="14">
         <f t="shared" si="16"/>
-        <v>0.15081789229878401</v>
-      </c>
-      <c r="CB14" s="13">
+        <v>0.27869359072536048</v>
+      </c>
+      <c r="CL14" s="14">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="CC14" s="13">
+        <v>5.9774635928424726E-2</v>
+      </c>
+      <c r="CM14" s="14">
         <f t="shared" si="16"/>
-        <v>3.5176606832657835E-3</v>
-      </c>
-      <c r="CD14" s="13">
-        <f t="shared" si="16"/>
-        <v>0.10291479820627801</v>
-      </c>
-      <c r="CE14" s="13">
-        <f t="shared" si="16"/>
-        <v>0.29906237260497348</v>
-      </c>
-      <c r="CF14" s="13">
-        <f t="shared" si="16"/>
-        <v>5.1671422747655918E-2</v>
-      </c>
-      <c r="CG14" s="13">
-        <f t="shared" si="16"/>
-        <v>0.21154708520179372</v>
-      </c>
-      <c r="CI14" s="141" t="s">
-        <v>13</v>
-      </c>
-      <c r="CJ14" s="145">
-        <f t="shared" si="4"/>
-        <v>3.7470224924993328E-2</v>
-      </c>
-      <c r="CK14" s="146">
+        <v>0.34109161825145057</v>
+      </c>
+      <c r="CO14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="CP14" s="14">
         <f t="shared" si="5"/>
-        <v>0.2870501038876801</v>
-      </c>
-      <c r="CL14" s="146">
+        <v>-0.31891394194968881</v>
+      </c>
+      <c r="CQ14" s="14">
         <f t="shared" si="6"/>
-        <v>4.7822073285303877E-2</v>
-      </c>
-      <c r="CM14" s="147">
+        <v>0.21891895479693577</v>
+      </c>
+      <c r="CR14" s="49">
         <f t="shared" si="7"/>
-        <v>0.31663106331600865</v>
-      </c>
-      <c r="CO14" s="141" t="s">
-        <v>13</v>
-      </c>
-      <c r="CP14" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.27916083839101535</v>
-      </c>
-      <c r="CQ14" s="146">
-        <f t="shared" si="9"/>
-        <v>0.23922803060237621</v>
-      </c>
-      <c r="CR14" s="49">
+        <v>5.1098760368070246E-3</v>
+      </c>
+      <c r="CS14" s="49">
+        <f t="shared" si="7"/>
+        <v>0.75865581156430628</v>
+      </c>
+      <c r="CU14" s="14"/>
+      <c r="CW14" s="107">
         <f t="shared" si="10"/>
-        <v>0.12659733841535062</v>
-      </c>
-      <c r="CS14" s="153">
-        <f t="shared" si="10"/>
-        <v>0.74006417316866091</v>
-      </c>
-      <c r="CU14" s="14"/>
-      <c r="CW14" s="157">
-        <f t="shared" si="13"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CY14" s="14"/>
     </row>
@@ -9305,25 +9211,25 @@
       <c r="R15" s="23">
         <v>1</v>
       </c>
-      <c r="T15" s="107"/>
-      <c r="U15" s="108">
+      <c r="T15" s="112"/>
+      <c r="U15" s="113">
         <v>51</v>
       </c>
-      <c r="V15" s="108">
+      <c r="V15" s="113">
         <v>66</v>
       </c>
-      <c r="W15" s="108">
+      <c r="W15" s="113">
         <v>3</v>
       </c>
-      <c r="X15" s="108">
+      <c r="X15" s="113">
         <v>5</v>
       </c>
-      <c r="Y15" s="109"/>
-      <c r="Z15" s="109"/>
-      <c r="AA15" s="109"/>
-      <c r="AB15" s="109"/>
-      <c r="AC15" s="109"/>
-      <c r="AD15" s="110"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="114"/>
+      <c r="AA15" s="114"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="123"/>
       <c r="AL15" s="39" t="s">
         <v>14</v>
       </c>
@@ -9339,7 +9245,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="80">
+      <c r="AP15" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9381,35 +9287,35 @@
         <v>13</v>
       </c>
       <c r="BE15" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BF15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="BG15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH15" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="BI15" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.977491961414791</v>
       </c>
       <c r="BJ15" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.65536723163841804</v>
       </c>
       <c r="BK15" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL15" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM15" s="45"/>
@@ -9445,79 +9351,79 @@
         <v>12</v>
       </c>
       <c r="BZ15" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="CA15" s="13">
+        <f t="shared" si="13"/>
+        <v>3.448613376835237E-2</v>
+      </c>
+      <c r="CB15" s="13">
+        <f t="shared" si="13"/>
+        <v>1.0331702011963037E-3</v>
+      </c>
+      <c r="CC15" s="13">
+        <f t="shared" si="13"/>
+        <v>0.11048758383179265</v>
+      </c>
+      <c r="CD15" s="13">
+        <f t="shared" si="13"/>
+        <v>3.6716357978216131E-2</v>
+      </c>
+      <c r="CE15" s="13">
+        <f t="shared" si="13"/>
+        <v>0.18720072278271344</v>
+      </c>
+      <c r="CF15" s="13">
+        <f t="shared" si="13"/>
+        <v>9.8228178487175632E-2</v>
+      </c>
+      <c r="CG15" s="13">
+        <f t="shared" si="13"/>
+        <v>0.26957536515585007</v>
+      </c>
+      <c r="CI15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CJ15" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA15" s="13">
+        <v>4.6465120252593368E-2</v>
+      </c>
+      <c r="CK15" s="14">
         <f t="shared" si="16"/>
-        <v>7.5018537742844435E-2</v>
-      </c>
-      <c r="CB15" s="13">
+        <v>0.22937862337251086</v>
+      </c>
+      <c r="CL15" s="14">
         <f t="shared" si="16"/>
-        <v>9.3430223935933685E-4</v>
-      </c>
-      <c r="CC15" s="13">
+        <v>6.9744456595071197E-2</v>
+      </c>
+      <c r="CM15" s="14">
         <f t="shared" si="16"/>
-        <v>0.18679371199762718</v>
-      </c>
-      <c r="CD15" s="13">
-        <f t="shared" si="16"/>
-        <v>3.3406113537117907E-2</v>
-      </c>
-      <c r="CE15" s="13">
-        <f t="shared" si="16"/>
-        <v>0.19241762604208018</v>
-      </c>
-      <c r="CF15" s="13">
-        <f t="shared" si="16"/>
-        <v>7.9734021437078209E-2</v>
-      </c>
-      <c r="CG15" s="13">
-        <f t="shared" si="16"/>
-        <v>0.2876637554585153</v>
-      </c>
-      <c r="CI15" s="141" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ15" s="145">
-        <f t="shared" si="4"/>
-        <v>3.821208293682115E-2</v>
-      </c>
-      <c r="CK15" s="146">
+        <v>0.28298043267470857</v>
+      </c>
+      <c r="CO15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CP15" s="14">
         <f t="shared" si="5"/>
-        <v>0.23015959139317252</v>
-      </c>
-      <c r="CL15" s="146">
+        <v>-0.23651531242211521</v>
+      </c>
+      <c r="CQ15" s="14">
         <f t="shared" si="6"/>
-        <v>6.5579875068584606E-2</v>
-      </c>
-      <c r="CM15" s="147">
+        <v>0.15963416677743966</v>
+      </c>
+      <c r="CR15" s="49">
         <f t="shared" si="7"/>
-        <v>0.36960739060565001</v>
-      </c>
-      <c r="CO15" s="141" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP15" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.33139530766882885</v>
-      </c>
-      <c r="CQ15" s="146">
-        <f t="shared" si="9"/>
-        <v>0.1645797163245879</v>
-      </c>
-      <c r="CR15" s="49">
+        <v>0.12055679783934356</v>
+      </c>
+      <c r="CS15" s="49">
+        <f t="shared" si="7"/>
+        <v>0.67559318872934293</v>
+      </c>
+      <c r="CU15" s="14"/>
+      <c r="CW15" s="107">
         <f t="shared" si="10"/>
-        <v>6.4782518596586777E-2</v>
-      </c>
-      <c r="CS15" s="153">
-        <f t="shared" si="10"/>
-        <v>0.65172457365413328</v>
-      </c>
-      <c r="CU15" s="14"/>
-      <c r="CW15" s="157">
-        <f t="shared" si="13"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CY15" s="14"/>
     </row>
@@ -9573,25 +9479,25 @@
       <c r="R16" s="23">
         <v>1</v>
       </c>
-      <c r="T16" s="107"/>
-      <c r="U16" s="108">
+      <c r="T16" s="112"/>
+      <c r="U16" s="113">
         <v>52</v>
       </c>
-      <c r="V16" s="108">
+      <c r="V16" s="113">
         <v>70</v>
       </c>
-      <c r="W16" s="108">
+      <c r="W16" s="113">
         <v>4</v>
       </c>
-      <c r="X16" s="108">
+      <c r="X16" s="113">
         <v>6</v>
       </c>
-      <c r="Y16" s="109"/>
-      <c r="Z16" s="109"/>
-      <c r="AA16" s="109"/>
-      <c r="AB16" s="109"/>
-      <c r="AC16" s="109"/>
-      <c r="AD16" s="110"/>
+      <c r="Y16" s="114"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="114"/>
+      <c r="AB16" s="114"/>
+      <c r="AC16" s="114"/>
+      <c r="AD16" s="123"/>
       <c r="AL16" s="39" t="s">
         <v>15</v>
       </c>
@@ -9607,7 +9513,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP16" s="80">
+      <c r="AP16" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -9649,35 +9555,35 @@
         <v>14</v>
       </c>
       <c r="BE16" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.80064308681672025</v>
       </c>
       <c r="BF16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="BG16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH16" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="BI16" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.932475884244373</v>
       </c>
       <c r="BJ16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.50847457627118642</v>
       </c>
       <c r="BK16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BL16" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM16" s="45"/>
@@ -9713,79 +9619,79 @@
         <v>13</v>
       </c>
       <c r="BZ16" s="13">
+        <f t="shared" si="14"/>
+        <v>1.2640603566529492E-2</v>
+      </c>
+      <c r="CA16" s="13">
+        <f t="shared" si="13"/>
+        <v>6.5679012345679008E-2</v>
+      </c>
+      <c r="CB16" s="13">
+        <f t="shared" si="13"/>
+        <v>1.5203475080018286E-3</v>
+      </c>
+      <c r="CC16" s="13">
+        <f t="shared" si="13"/>
+        <v>1.3443072702331967E-2</v>
+      </c>
+      <c r="CD16" s="13">
+        <f t="shared" si="13"/>
+        <v>8.6351175876496919E-2</v>
+      </c>
+      <c r="CE16" s="13">
+        <f t="shared" si="13"/>
+        <v>0.28117154811715483</v>
+      </c>
+      <c r="CF16" s="13">
+        <f t="shared" si="13"/>
+        <v>5.5739912470542982E-2</v>
+      </c>
+      <c r="CG16" s="13">
+        <f t="shared" si="13"/>
+        <v>0.20497042273842159</v>
+      </c>
+      <c r="CI16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="CJ16" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA16" s="13">
+        <v>4.600739468234806E-2</v>
+      </c>
+      <c r="CK16" s="14">
         <f t="shared" si="16"/>
-        <v>0.14287317620650955</v>
-      </c>
-      <c r="CB16" s="13">
+        <v>0.17887137325098965</v>
+      </c>
+      <c r="CL16" s="14">
         <f t="shared" si="16"/>
-        <v>1.3748597081930411E-3</v>
-      </c>
-      <c r="CC16" s="13">
+        <v>9.3115201316014168E-2</v>
+      </c>
+      <c r="CM16" s="14">
         <f t="shared" si="16"/>
-        <v>2.2727272727272735E-2</v>
-      </c>
-      <c r="CD16" s="13">
-        <f t="shared" si="16"/>
-        <v>7.85659946747813E-2</v>
-      </c>
-      <c r="CE16" s="13">
-        <f t="shared" si="16"/>
-        <v>0.2890072270825409</v>
-      </c>
-      <c r="CF16" s="13">
-        <f t="shared" si="16"/>
-        <v>4.5245340433624957E-2</v>
-      </c>
-      <c r="CG16" s="13">
-        <f t="shared" si="16"/>
-        <v>0.2187238493723849</v>
-      </c>
-      <c r="CI16" s="141" t="s">
-        <v>15</v>
-      </c>
-      <c r="CJ16" s="145">
-        <f t="shared" si="4"/>
-        <v>1.2756956918907984E-2</v>
-      </c>
-      <c r="CK16" s="146">
+        <v>0.32461104933294577</v>
+      </c>
+      <c r="CO16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP16" s="14">
         <f t="shared" si="5"/>
-        <v>0.25358477950774899</v>
-      </c>
-      <c r="CL16" s="146">
+        <v>-0.27860365465059772</v>
+      </c>
+      <c r="CQ16" s="14">
         <f t="shared" si="6"/>
-        <v>6.2727403259126291E-2</v>
-      </c>
-      <c r="CM16" s="147">
+        <v>8.5756171934975478E-2</v>
+      </c>
+      <c r="CR16" s="49">
         <f t="shared" si="7"/>
-        <v>0.30570504905725104</v>
-      </c>
-      <c r="CO16" s="141" t="s">
-        <v>15</v>
-      </c>
-      <c r="CP16" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.29294809213834305</v>
-      </c>
-      <c r="CQ16" s="146">
-        <f t="shared" si="9"/>
-        <v>0.1908573762486227</v>
-      </c>
-      <c r="CR16" s="49">
+        <v>6.1587739956845307E-2</v>
+      </c>
+      <c r="CS16" s="49">
+        <f t="shared" si="7"/>
+        <v>0.5720843422545111</v>
+      </c>
+      <c r="CU16" s="14"/>
+      <c r="CW16" s="107">
         <f t="shared" si="10"/>
-        <v>0.11028135745546304</v>
-      </c>
-      <c r="CS16" s="153">
-        <f t="shared" si="10"/>
-        <v>0.68282183253167106</v>
-      </c>
-      <c r="CU16" s="14"/>
-      <c r="CW16" s="157">
-        <f t="shared" si="13"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CY16" s="14"/>
     </row>
@@ -9841,25 +9747,25 @@
       <c r="R17" s="23">
         <v>2</v>
       </c>
-      <c r="T17" s="107"/>
-      <c r="U17" s="108">
+      <c r="T17" s="112"/>
+      <c r="U17" s="113">
         <v>79</v>
       </c>
-      <c r="V17" s="108">
+      <c r="V17" s="113">
         <v>72</v>
       </c>
-      <c r="W17" s="108">
+      <c r="W17" s="113">
         <v>8</v>
       </c>
-      <c r="X17" s="108">
+      <c r="X17" s="113">
         <v>6</v>
       </c>
-      <c r="Y17" s="109"/>
-      <c r="Z17" s="109"/>
-      <c r="AA17" s="109"/>
-      <c r="AB17" s="109"/>
-      <c r="AC17" s="109"/>
-      <c r="AD17" s="110"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="123"/>
       <c r="AL17" s="39" t="s">
         <v>16</v>
       </c>
@@ -9875,7 +9781,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP17" s="80">
+      <c r="AP17" s="79">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -9917,35 +9823,35 @@
         <v>15</v>
       </c>
       <c r="BE17" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="BF17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.10169491525423729</v>
       </c>
       <c r="BG17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH17" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI17" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="BJ17" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.42372881355932202</v>
       </c>
       <c r="BK17" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="BL17" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM17" s="45"/>
@@ -9981,79 +9887,79 @@
         <v>14</v>
       </c>
       <c r="BZ17" s="13">
+        <f t="shared" si="14"/>
+        <v>9.9558080808080807E-3</v>
+      </c>
+      <c r="CA17" s="13">
+        <f t="shared" si="13"/>
+        <v>5.7670454545454553E-2</v>
+      </c>
+      <c r="CB17" s="13">
+        <f t="shared" si="13"/>
+        <v>4.1982323232323216E-3</v>
+      </c>
+      <c r="CC17" s="13">
+        <f t="shared" si="13"/>
+        <v>3.8358585858585863E-2</v>
+      </c>
+      <c r="CD17" s="13">
+        <f t="shared" si="13"/>
+        <v>8.8060808305524665E-2</v>
+      </c>
+      <c r="CE17" s="13">
+        <f t="shared" si="13"/>
+        <v>0.24026696329254732</v>
+      </c>
+      <c r="CF17" s="13">
+        <f t="shared" si="13"/>
+        <v>8.755760368663594E-2</v>
+      </c>
+      <c r="CG17" s="13">
+        <f t="shared" si="13"/>
+        <v>0.23309232480533928</v>
+      </c>
+      <c r="CI17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ17" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA17" s="13">
+        <v>2.0052279024729475E-2</v>
+      </c>
+      <c r="CK17" s="14">
         <f t="shared" si="16"/>
-        <v>0.12545196280991736</v>
-      </c>
-      <c r="CB17" s="13">
+        <v>0.19275049908896524</v>
+      </c>
+      <c r="CL17" s="14">
         <f t="shared" si="16"/>
-        <v>3.7964876033057841E-3</v>
-      </c>
-      <c r="CC17" s="13">
+        <v>8.7862478252151099E-2</v>
+      </c>
+      <c r="CM17" s="14">
         <f t="shared" si="16"/>
-        <v>6.4850206611570246E-2</v>
-      </c>
-      <c r="CD17" s="13">
-        <f t="shared" si="16"/>
-        <v>8.0121491411814003E-2</v>
-      </c>
-      <c r="CE17" s="13">
-        <f t="shared" si="16"/>
-        <v>0.2469627147046502</v>
-      </c>
-      <c r="CF17" s="13">
-        <f t="shared" si="16"/>
-        <v>7.1072475911185581E-2</v>
-      </c>
-      <c r="CG17" s="13">
-        <f t="shared" si="16"/>
-        <v>0.24873271889400922</v>
-      </c>
-      <c r="CI17" s="141" t="s">
-        <v>16</v>
-      </c>
-      <c r="CJ17" s="145">
-        <f t="shared" si="4"/>
-        <v>2.9394655044401474E-2</v>
-      </c>
-      <c r="CK17" s="146">
+        <v>0.27469752920662893</v>
+      </c>
+      <c r="CO17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="CP17" s="14">
         <f t="shared" si="5"/>
-        <v>0.32823432532516222</v>
-      </c>
-      <c r="CL17" s="146">
+        <v>-0.25464525018189943</v>
+      </c>
+      <c r="CQ17" s="14">
         <f t="shared" si="6"/>
-        <v>5.2783147464746105E-2</v>
-      </c>
-      <c r="CM17" s="147">
+        <v>0.10488802083681414</v>
+      </c>
+      <c r="CR17" s="49">
         <f t="shared" si="7"/>
-        <v>0.39488444441037213</v>
-      </c>
-      <c r="CO17" s="141" t="s">
-        <v>16</v>
-      </c>
-      <c r="CP17" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.36548978936597065</v>
-      </c>
-      <c r="CQ17" s="146">
-        <f t="shared" si="9"/>
-        <v>0.27545117786041612</v>
-      </c>
-      <c r="CR17" s="49">
+        <v>9.5155337659253381E-2</v>
+      </c>
+      <c r="CS17" s="49">
+        <f t="shared" si="7"/>
+        <v>0.59888955827293278</v>
+      </c>
+      <c r="CU17" s="14"/>
+      <c r="CW17" s="107">
         <f t="shared" si="10"/>
-        <v>2.4434750694249968E-2</v>
-      </c>
-      <c r="CS17" s="153">
-        <f t="shared" si="10"/>
-        <v>0.78293102626360278</v>
-      </c>
-      <c r="CU17" s="14"/>
-      <c r="CW17" s="157">
-        <f t="shared" si="13"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CY17" s="14"/>
     </row>
@@ -10109,25 +10015,25 @@
       <c r="R18" s="23">
         <v>0</v>
       </c>
-      <c r="T18" s="107"/>
-      <c r="U18" s="108">
+      <c r="T18" s="112"/>
+      <c r="U18" s="113">
         <v>108</v>
       </c>
-      <c r="V18" s="108">
+      <c r="V18" s="113">
         <v>90</v>
       </c>
-      <c r="W18" s="108">
+      <c r="W18" s="113">
         <v>15</v>
       </c>
-      <c r="X18" s="108">
+      <c r="X18" s="113">
         <v>9</v>
       </c>
-      <c r="Y18" s="109"/>
-      <c r="Z18" s="109"/>
-      <c r="AA18" s="109"/>
-      <c r="AB18" s="109"/>
-      <c r="AC18" s="109"/>
-      <c r="AD18" s="110"/>
+      <c r="Y18" s="114"/>
+      <c r="Z18" s="114"/>
+      <c r="AA18" s="114"/>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="114"/>
+      <c r="AD18" s="123"/>
       <c r="AL18" s="39" t="s">
         <v>17</v>
       </c>
@@ -10143,7 +10049,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="80">
+      <c r="AP18" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10185,35 +10091,35 @@
         <v>16</v>
       </c>
       <c r="BE18" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.57234726688102899</v>
       </c>
       <c r="BF18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.19209039548022599</v>
       </c>
       <c r="BG18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH18" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BI18" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BJ18" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.48022598870056499</v>
       </c>
       <c r="BK18" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.57692307692307687</v>
       </c>
       <c r="BL18" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BM18" s="45"/>
@@ -10249,79 +10155,79 @@
         <v>15</v>
       </c>
       <c r="BZ18" s="13">
+        <f t="shared" si="14"/>
+        <v>1.3321686466340554E-2</v>
+      </c>
+      <c r="CA18" s="13">
+        <f t="shared" si="13"/>
+        <v>6.7798742138364787E-2</v>
+      </c>
+      <c r="CB18" s="13">
+        <f t="shared" si="13"/>
+        <v>6.6387141858840061E-4</v>
+      </c>
+      <c r="CC18" s="13">
+        <f t="shared" si="13"/>
+        <v>6.8483577917540219E-3</v>
+      </c>
+      <c r="CD18" s="13">
+        <f t="shared" si="13"/>
+        <v>2.9398762157382848E-2</v>
+      </c>
+      <c r="CE18" s="13">
+        <f t="shared" si="13"/>
+        <v>0.1856763925729443</v>
+      </c>
+      <c r="CF18" s="13">
+        <f t="shared" si="13"/>
+        <v>9.5195991747715883E-2</v>
+      </c>
+      <c r="CG18" s="13">
+        <f t="shared" si="13"/>
+        <v>0.27062334217506634</v>
+      </c>
+      <c r="CI18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CJ18" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA18" s="13">
+        <v>3.4714767322780435E-2</v>
+      </c>
+      <c r="CK18" s="14">
         <f t="shared" si="16"/>
-        <v>0.14748427672955977</v>
-      </c>
-      <c r="CB18" s="13">
+        <v>0.28705082821573485</v>
+      </c>
+      <c r="CL18" s="14">
         <f t="shared" si="16"/>
-        <v>6.0034305317324265E-4</v>
-      </c>
-      <c r="CC18" s="13">
+        <v>6.8608550252356154E-2</v>
+      </c>
+      <c r="CM18" s="14">
         <f t="shared" si="16"/>
-        <v>1.1578044596912525E-2</v>
-      </c>
-      <c r="CD18" s="13">
-        <f t="shared" si="16"/>
-        <v>2.6748251748251749E-2</v>
-      </c>
-      <c r="CE18" s="13">
-        <f t="shared" si="16"/>
-        <v>0.19085081585081584</v>
-      </c>
-      <c r="CF18" s="13">
-        <f t="shared" si="16"/>
-        <v>7.7272727272727257E-2</v>
-      </c>
-      <c r="CG18" s="13">
-        <f t="shared" si="16"/>
-        <v>0.28878205128205131</v>
-      </c>
-      <c r="CI18" s="141" t="s">
-        <v>17</v>
-      </c>
-      <c r="CJ18" s="145">
-        <f t="shared" si="4"/>
-        <v>6.753683074715992E-3</v>
-      </c>
-      <c r="CK18" s="146">
+        <v>0.34092340947929145</v>
+      </c>
+      <c r="CO18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="CP18" s="14">
         <f t="shared" si="5"/>
-        <v>0.20147774728152507</v>
-      </c>
-      <c r="CL18" s="146">
+        <v>-0.306208642156511</v>
+      </c>
+      <c r="CQ18" s="14">
         <f t="shared" si="6"/>
-        <v>7.7675060890172079E-2</v>
-      </c>
-      <c r="CM18" s="147">
+        <v>0.2184422779633787</v>
+      </c>
+      <c r="CR18" s="49">
         <f t="shared" si="7"/>
-        <v>0.33928569642286066</v>
-      </c>
-      <c r="CO18" s="141" t="s">
-        <v>17</v>
-      </c>
-      <c r="CP18" s="145">
-        <f t="shared" si="8"/>
-        <v>-0.33253201334814469</v>
-      </c>
-      <c r="CQ18" s="146">
-        <f t="shared" si="9"/>
-        <v>0.12380268639135299</v>
-      </c>
-      <c r="CR18" s="49">
+        <v>2.2910994333440109E-2</v>
+      </c>
+      <c r="CS18" s="49">
+        <f t="shared" si="7"/>
+        <v>0.75798795005442132</v>
+      </c>
+      <c r="CU18" s="14"/>
+      <c r="CW18" s="107">
         <f t="shared" si="10"/>
-        <v>6.3437329151276978E-2</v>
-      </c>
-      <c r="CS18" s="153">
-        <f t="shared" si="10"/>
-        <v>0.60346860794955037</v>
-      </c>
-      <c r="CU18" s="14"/>
-      <c r="CW18" s="157">
-        <f t="shared" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CY18" s="14"/>
     </row>
@@ -10329,7 +10235,7 @@
       <c r="A19" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="59" t="s">
+      <c r="B19" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="24">
@@ -10377,41 +10283,41 @@
       <c r="R19" s="23">
         <v>0</v>
       </c>
-      <c r="T19" s="107"/>
-      <c r="U19" s="108">
+      <c r="T19" s="112"/>
+      <c r="U19" s="113">
         <v>116</v>
       </c>
-      <c r="V19" s="108">
+      <c r="V19" s="113">
         <v>96</v>
       </c>
-      <c r="W19" s="108">
+      <c r="W19" s="113">
         <v>26</v>
       </c>
-      <c r="X19" s="108">
+      <c r="X19" s="113">
         <v>9</v>
       </c>
-      <c r="Y19" s="109"/>
-      <c r="Z19" s="109"/>
-      <c r="AA19" s="109"/>
-      <c r="AB19" s="109"/>
-      <c r="AC19" s="109"/>
-      <c r="AD19" s="110"/>
-      <c r="AL19" s="73" t="s">
+      <c r="Y19" s="114"/>
+      <c r="Z19" s="114"/>
+      <c r="AA19" s="114"/>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="114"/>
+      <c r="AD19" s="123"/>
+      <c r="AL19" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AM19" s="84">
+      <c r="AM19" s="83">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN19" s="85">
+      <c r="AN19" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="85">
+      <c r="AO19" s="84">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="86">
+      <c r="AP19" s="85">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10453,35 +10359,35 @@
         <v>17</v>
       </c>
       <c r="BE19" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="BF19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>5.0847457627118647E-2</v>
       </c>
       <c r="BG19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH19" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI19" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="BJ19" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.29943502824858759</v>
       </c>
       <c r="BK19" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BL19" s="50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM19" s="45"/>
@@ -10517,79 +10423,79 @@
         <v>16</v>
       </c>
       <c r="BZ19" s="13">
+        <f t="shared" si="14"/>
+        <v>6.1704068600620336E-3</v>
+      </c>
+      <c r="CA19" s="13">
+        <f t="shared" si="13"/>
+        <v>4.7068965517241393E-2</v>
+      </c>
+      <c r="CB19" s="13">
+        <f t="shared" si="13"/>
+        <v>6.5863893450100342E-3</v>
+      </c>
+      <c r="CC19" s="13">
+        <f t="shared" si="13"/>
+        <v>7.1340996168582374E-2</v>
+      </c>
+      <c r="CD19" s="13">
+        <f t="shared" si="13"/>
+        <v>5.6992337164750967E-2</v>
+      </c>
+      <c r="CE19" s="13">
+        <f t="shared" si="13"/>
+        <v>0.21597096188747736</v>
+      </c>
+      <c r="CF19" s="13">
+        <f t="shared" si="13"/>
+        <v>8.8122605363984668E-2</v>
+      </c>
+      <c r="CG19" s="13">
+        <f t="shared" si="13"/>
+        <v>0.24979582577132489</v>
+      </c>
+      <c r="CI19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="CJ19" s="14">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="CA19" s="13">
+        <v>1.2959413985343754E-2</v>
+      </c>
+      <c r="CK19" s="14">
         <f t="shared" si="16"/>
-        <v>0.10239028213166147</v>
-      </c>
-      <c r="CB19" s="13">
+        <v>0.14348813538190636</v>
+      </c>
+      <c r="CL19" s="14">
         <f t="shared" si="16"/>
-        <v>5.9561128526645765E-3</v>
-      </c>
-      <c r="CC19" s="13">
+        <v>0.10795967942596776</v>
+      </c>
+      <c r="CM19" s="14">
         <f t="shared" si="16"/>
-        <v>0.12061128526645767</v>
-      </c>
-      <c r="CD19" s="13">
-        <f t="shared" si="16"/>
-        <v>5.1854066985645937E-2</v>
-      </c>
-      <c r="CE19" s="13">
-        <f t="shared" si="16"/>
-        <v>0.22198963317384374</v>
-      </c>
-      <c r="CF19" s="13">
-        <f t="shared" si="16"/>
-        <v>7.153110047846889E-2</v>
-      </c>
-      <c r="CG19" s="13">
-        <f t="shared" si="16"/>
-        <v>0.26655701754385969</v>
-      </c>
-      <c r="CI19" s="141" t="s">
-        <v>21</v>
-      </c>
-      <c r="CJ19" s="148">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="CK19" s="149">
+        <v>0.30248428438531272</v>
+      </c>
+      <c r="CO19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="CP19" s="14">
         <f t="shared" si="5"/>
-        <v>0.32022064997972061</v>
-      </c>
-      <c r="CL19" s="149">
+        <v>-0.28952487039996899</v>
+      </c>
+      <c r="CQ19" s="14">
         <f t="shared" si="6"/>
-        <v>4.2165357415780522E-2</v>
-      </c>
-      <c r="CM19" s="150">
+        <v>3.5528455955938593E-2</v>
+      </c>
+      <c r="CR19" s="49">
         <f t="shared" si="7"/>
-        <v>0.2599525201746497</v>
-      </c>
-      <c r="CO19" s="141" t="s">
-        <v>21</v>
-      </c>
-      <c r="CP19" s="148">
-        <f t="shared" si="8"/>
-        <v>-0.2599525201746497</v>
-      </c>
-      <c r="CQ19" s="149">
-        <f t="shared" si="9"/>
-        <v>0.27805529256394007</v>
-      </c>
-      <c r="CR19" s="154">
+        <v>4.6286262883317296E-2</v>
+      </c>
+      <c r="CS19" s="49">
+        <f t="shared" si="7"/>
+        <v>0.50171138542018112</v>
+      </c>
+      <c r="CU19" s="14"/>
+      <c r="CW19" s="108">
         <f t="shared" si="10"/>
-        <v>0.14932866403198614</v>
-      </c>
-      <c r="CS19" s="155">
-        <f t="shared" si="10"/>
-        <v>0.78601276296757072</v>
-      </c>
-      <c r="CU19" s="14"/>
-      <c r="CW19" s="158">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="CY19" s="14"/>
     </row>
@@ -10645,33 +10551,33 @@
       <c r="R20" s="23">
         <v>2</v>
       </c>
-      <c r="T20" s="107"/>
-      <c r="U20" s="109"/>
-      <c r="V20" s="109"/>
-      <c r="W20" s="109"/>
-      <c r="X20" s="109"/>
-      <c r="Y20" s="109"/>
-      <c r="Z20" s="109"/>
-      <c r="AA20" s="109"/>
-      <c r="AB20" s="109"/>
-      <c r="AC20" s="109"/>
-      <c r="AD20" s="110"/>
+      <c r="T20" s="112"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="114"/>
+      <c r="W20" s="114"/>
+      <c r="X20" s="114"/>
+      <c r="Y20" s="114"/>
+      <c r="Z20" s="114"/>
+      <c r="AA20" s="114"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="123"/>
       <c r="AL20" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM20" s="77">
+      <c r="AM20" s="76">
         <f t="shared" si="0"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN20" s="78">
+      <c r="AN20" s="77">
         <f t="shared" si="1"/>
         <v>0.24293785310734464</v>
       </c>
-      <c r="AO20" s="78">
+      <c r="AO20" s="77">
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP20" s="79">
+      <c r="AP20" s="78">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10713,35 +10619,35 @@
         <v>21</v>
       </c>
       <c r="BE20" s="54">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="BF20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BG20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BH20" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="BI20" s="54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BJ20" s="54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.5423728813559322</v>
       </c>
       <c r="BK20" s="54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.30769230769230771</v>
       </c>
       <c r="BL20" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BM20" s="45"/>
@@ -10777,36 +10683,36 @@
         <v>17</v>
       </c>
       <c r="BZ20" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.2045378712045376E-2</v>
       </c>
       <c r="CA20" s="13">
-        <f t="shared" si="16"/>
-        <v>0.14038356538356536</v>
+        <f t="shared" si="13"/>
+        <v>6.4534534534534532E-2</v>
       </c>
       <c r="CB20" s="13">
-        <f t="shared" si="16"/>
-        <v>7.644007644007631E-4</v>
+        <f t="shared" si="13"/>
+        <v>8.4528973417862159E-4</v>
       </c>
       <c r="CC20" s="13">
-        <f t="shared" si="16"/>
-        <v>2.8746928746928756E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.7003670337003677E-2</v>
       </c>
       <c r="CD20" s="13">
-        <f t="shared" si="16"/>
-        <v>1.4160839160839163E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.5564050553908569E-2</v>
       </c>
       <c r="CE20" s="13">
-        <f t="shared" si="16"/>
-        <v>0.14280131633072812</v>
+        <f t="shared" si="13"/>
+        <v>0.13892963020752069</v>
       </c>
       <c r="CF20" s="13">
-        <f t="shared" si="16"/>
-        <v>9.9465240641711222E-2</v>
+        <f t="shared" si="13"/>
+        <v>0.12253601705934362</v>
       </c>
       <c r="CG20" s="13">
-        <f t="shared" si="16"/>
-        <v>0.32307692307692309</v>
+        <f t="shared" si="13"/>
+        <v>0.30276174130129507</v>
       </c>
       <c r="CR20" s="13"/>
       <c r="CS20" s="13"/>
@@ -10863,19 +10769,19 @@
       <c r="R21" s="23">
         <v>0</v>
       </c>
-      <c r="T21" s="112" t="s">
+      <c r="T21" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="U21" s="109"/>
-      <c r="V21" s="109"/>
-      <c r="W21" s="109"/>
-      <c r="X21" s="109"/>
-      <c r="Y21" s="109"/>
-      <c r="Z21" s="109"/>
-      <c r="AA21" s="109"/>
-      <c r="AB21" s="109"/>
-      <c r="AC21" s="109"/>
-      <c r="AD21" s="110"/>
+      <c r="U21" s="114"/>
+      <c r="V21" s="114"/>
+      <c r="W21" s="114"/>
+      <c r="X21" s="114"/>
+      <c r="Y21" s="114"/>
+      <c r="Z21" s="114"/>
+      <c r="AA21" s="114"/>
+      <c r="AB21" s="114"/>
+      <c r="AC21" s="114"/>
+      <c r="AD21" s="123"/>
       <c r="AL21" s="39" t="s">
         <v>2</v>
       </c>
@@ -10891,7 +10797,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP21" s="80">
+      <c r="AP21" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10929,21 +10835,21 @@
         <v>0</v>
       </c>
       <c r="BC21" s="45"/>
-      <c r="BD21" s="95" t="s">
+      <c r="BD21" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="BE21" s="97" t="s">
+      <c r="BE21" s="135" t="s">
         <v>111</v>
       </c>
-      <c r="BF21" s="97"/>
-      <c r="BG21" s="97"/>
-      <c r="BH21" s="97"/>
-      <c r="BI21" s="97" t="s">
+      <c r="BF21" s="135"/>
+      <c r="BG21" s="135"/>
+      <c r="BH21" s="135"/>
+      <c r="BI21" s="135" t="s">
         <v>112</v>
       </c>
-      <c r="BJ21" s="97"/>
-      <c r="BK21" s="97"/>
-      <c r="BL21" s="98"/>
+      <c r="BJ21" s="135"/>
+      <c r="BK21" s="135"/>
+      <c r="BL21" s="136"/>
       <c r="BM21" s="45"/>
       <c r="BN21" s="45"/>
       <c r="BO21" s="4" t="s">
@@ -10977,44 +10883,44 @@
         <v>21</v>
       </c>
       <c r="BZ21" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1.3716637272192829E-2</v>
       </c>
       <c r="CA21" s="13">
-        <f t="shared" si="16"/>
-        <v>0.15033910533910538</v>
+        <f t="shared" si="13"/>
+        <v>6.9111111111111123E-2</v>
       </c>
       <c r="CB21" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CC21" s="13">
-        <f t="shared" si="16"/>
-        <v>4.6753246753246692E-3</v>
+        <f t="shared" si="13"/>
+        <v>2.765432098765429E-3</v>
       </c>
       <c r="CD21" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CE21" s="13">
-        <f t="shared" si="16"/>
-        <v>0.20939060939060941</v>
+        <f t="shared" si="13"/>
+        <v>0.20371352785145891</v>
       </c>
       <c r="CF21" s="13">
-        <f t="shared" si="16"/>
-        <v>5.2597402597402587E-2</v>
+        <f t="shared" si="13"/>
+        <v>6.4797271693823419E-2</v>
       </c>
       <c r="CG21" s="13">
-        <f t="shared" si="16"/>
-        <v>0.27554945054945057</v>
+        <f t="shared" si="13"/>
+        <v>0.25822281167108757</v>
       </c>
       <c r="CP21" s="13">
         <f>ABS(MIN(CP4:CP19))</f>
-        <v>0.38613752785638361</v>
+        <v>0.32256104466940322</v>
       </c>
       <c r="CQ21" s="13">
         <f>MAX(CQ4:CQ19)</f>
-        <v>0.45887778450658739</v>
+        <v>0.39117500165420849</v>
       </c>
     </row>
     <row r="22" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11069,31 +10975,31 @@
       <c r="R22" s="23">
         <v>1</v>
       </c>
-      <c r="T22" s="112" t="s">
+      <c r="T22" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="U22" s="109">
+      <c r="U22" s="114">
         <f>MIN(U4:U8)</f>
         <v>2</v>
       </c>
-      <c r="V22" s="109">
+      <c r="V22" s="114">
         <f>MIN(V16:V19)</f>
         <v>70</v>
       </c>
-      <c r="W22" s="109">
+      <c r="W22" s="114">
         <f>MIN(W18:W19)</f>
         <v>15</v>
       </c>
-      <c r="X22" s="109">
+      <c r="X22" s="114">
         <f>MIN(X4:X13)</f>
         <v>0</v>
       </c>
-      <c r="Y22" s="109"/>
-      <c r="Z22" s="109"/>
-      <c r="AA22" s="109"/>
-      <c r="AB22" s="109"/>
-      <c r="AC22" s="109"/>
-      <c r="AD22" s="110"/>
+      <c r="Y22" s="114"/>
+      <c r="Z22" s="114"/>
+      <c r="AA22" s="114"/>
+      <c r="AB22" s="114"/>
+      <c r="AC22" s="114"/>
+      <c r="AD22" s="123"/>
       <c r="AL22" s="39" t="s">
         <v>4</v>
       </c>
@@ -11109,7 +11015,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="80">
+      <c r="AP22" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -11147,7 +11053,7 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="BC22" s="45"/>
-      <c r="BD22" s="96"/>
+      <c r="BD22" s="134"/>
       <c r="BE22" s="47" t="s">
         <v>64</v>
       </c>
@@ -11279,31 +11185,31 @@
       <c r="R23" s="23">
         <v>1</v>
       </c>
-      <c r="T23" s="112" t="s">
-        <v>37</v>
-      </c>
-      <c r="U23" s="109">
+      <c r="T23" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="U23" s="114">
         <f>MIN(U9:U14)</f>
         <v>10</v>
       </c>
-      <c r="V23" s="109">
+      <c r="V23" s="114">
         <f>MIN(V9:V15)</f>
         <v>40</v>
       </c>
-      <c r="W23" s="109">
+      <c r="W23" s="114">
         <f>MIN(W16:W17)</f>
         <v>4</v>
       </c>
-      <c r="X23" s="109">
+      <c r="X23" s="114">
         <f>MIN(X14:X15)</f>
         <v>2</v>
       </c>
-      <c r="Y23" s="109"/>
-      <c r="Z23" s="109"/>
-      <c r="AA23" s="109"/>
-      <c r="AB23" s="109"/>
-      <c r="AC23" s="109"/>
-      <c r="AD23" s="110"/>
+      <c r="Y23" s="114"/>
+      <c r="Z23" s="114"/>
+      <c r="AA23" s="114"/>
+      <c r="AB23" s="114"/>
+      <c r="AC23" s="114"/>
+      <c r="AD23" s="123"/>
       <c r="AL23" s="39" t="s">
         <v>5</v>
       </c>
@@ -11319,7 +11225,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="80">
+      <c r="AP23" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -11395,40 +11301,40 @@
       <c r="BM23" s="45"/>
       <c r="BN23" s="45"/>
       <c r="BO23" s="38"/>
-      <c r="BP23" s="133" t="s">
+      <c r="BP23" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="BQ23" s="133"/>
-      <c r="BR23" s="133" t="s">
+      <c r="BQ23" s="130"/>
+      <c r="BR23" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="BS23" s="133"/>
-      <c r="BT23" s="133" t="s">
+      <c r="BS23" s="130"/>
+      <c r="BT23" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="BU23" s="133"/>
-      <c r="BV23" s="133" t="s">
+      <c r="BU23" s="130"/>
+      <c r="BV23" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="BW23" s="133"/>
+      <c r="BW23" s="130"/>
       <c r="BY23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="BZ23" s="13">
         <f t="shared" ref="BZ23:CG38" si="20">BP27*BP$24</f>
-        <v>1.2618595825426945E-2</v>
+        <v>1.3929618768328444E-2</v>
       </c>
       <c r="CA23" s="13">
         <f t="shared" si="20"/>
-        <v>0.15768500948766606</v>
+        <v>0.16011730205278593</v>
       </c>
       <c r="CB23" s="13">
         <f t="shared" si="20"/>
-        <v>4.3643263757115747E-2</v>
+        <v>7.42913000977517E-2</v>
       </c>
       <c r="CC23" s="13">
         <f t="shared" si="20"/>
-        <v>0.23007590132827324</v>
+        <v>0.20527859237536661</v>
       </c>
       <c r="CD23" s="13">
         <f t="shared" si="20"/>
@@ -11436,7 +11342,7 @@
       </c>
       <c r="CE23" s="13">
         <f t="shared" si="20"/>
-        <v>9.9999999999999978E-2</v>
+        <v>6.5624999999999989E-2</v>
       </c>
       <c r="CF23" s="13">
         <f t="shared" si="20"/>
@@ -11444,7 +11350,7 @@
       </c>
       <c r="CG23" s="13">
         <f t="shared" si="20"/>
-        <v>0.11666666666666667</v>
+        <v>0.10937500000000001</v>
       </c>
     </row>
     <row r="24" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11499,31 +11405,31 @@
       <c r="R24" s="23">
         <v>1</v>
       </c>
-      <c r="T24" s="112" t="s">
-        <v>107</v>
-      </c>
-      <c r="U24" s="109">
+      <c r="T24" s="115" t="s">
+        <v>37</v>
+      </c>
+      <c r="U24" s="114">
         <f>MIN(U15:U19)</f>
         <v>51</v>
       </c>
-      <c r="V24" s="109">
+      <c r="V24" s="114">
         <f>MIN(V4:V8)</f>
         <v>14</v>
       </c>
-      <c r="W24" s="109">
+      <c r="W24" s="114">
         <f>MIN(W4:W15)</f>
         <v>0</v>
       </c>
-      <c r="X24" s="109">
+      <c r="X24" s="114">
         <f>MIN(X16:X19)</f>
         <v>6</v>
       </c>
-      <c r="Y24" s="109"/>
-      <c r="Z24" s="109"/>
-      <c r="AA24" s="109"/>
-      <c r="AB24" s="109"/>
-      <c r="AC24" s="109"/>
-      <c r="AD24" s="110"/>
+      <c r="Y24" s="114"/>
+      <c r="Z24" s="114"/>
+      <c r="AA24" s="114"/>
+      <c r="AB24" s="114"/>
+      <c r="AC24" s="114"/>
+      <c r="AD24" s="123"/>
       <c r="AL24" s="39" t="s">
         <v>6</v>
       </c>
@@ -11539,7 +11445,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP24" s="80">
+      <c r="AP24" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11615,48 +11521,48 @@
       <c r="BM24" s="45"/>
       <c r="BN24" s="45"/>
       <c r="BO24" s="30"/>
-      <c r="BP24" s="136">
+      <c r="BP24" s="103">
         <f>AC37</f>
-        <v>0.39117647058823529</v>
-      </c>
-      <c r="BQ24" s="137">
+        <v>0.43181818181818177</v>
+      </c>
+      <c r="BQ24" s="104">
         <f>AC38</f>
-        <v>0.81470588235294117</v>
-      </c>
-      <c r="BR24" s="137">
+        <v>0.82727272727272727</v>
+      </c>
+      <c r="BR24" s="104">
         <f>AC39</f>
-        <v>6.7647058823529407E-2</v>
-      </c>
-      <c r="BS24" s="137">
+        <v>0.11515151515151514</v>
+      </c>
+      <c r="BS24" s="104">
         <f>AC40</f>
-        <v>0.28529411764705881</v>
-      </c>
-      <c r="BT24" s="137">
+        <v>0.25454545454545457</v>
+      </c>
+      <c r="BT24" s="104">
         <f>AD37</f>
         <v>0</v>
       </c>
-      <c r="BU24" s="137">
+      <c r="BU24" s="104">
         <f>AD38</f>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="BV24" s="137">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="BV24" s="104">
         <f>AD39</f>
-        <v>0.11666666666666665</v>
-      </c>
-      <c r="BW24" s="138">
+        <v>0.15833333333333333</v>
+      </c>
+      <c r="BW24" s="105">
         <f>AD40</f>
-        <v>0.46666666666666667</v>
+        <v>0.43750000000000006</v>
       </c>
       <c r="BY24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="BZ24" s="13">
         <f t="shared" si="20"/>
-        <v>1.5647058823529413E-2</v>
+        <v>1.7272727272727269E-2</v>
       </c>
       <c r="CA24" s="13">
         <f t="shared" si="20"/>
-        <v>0.42364705882352943</v>
+        <v>0.43018181818181822</v>
       </c>
       <c r="CB24" s="13">
         <f t="shared" si="20"/>
@@ -11664,7 +11570,7 @@
       </c>
       <c r="CC24" s="13">
         <f t="shared" si="20"/>
-        <v>0.13694117647058823</v>
+        <v>0.12218181818181821</v>
       </c>
       <c r="CD24" s="13">
         <f t="shared" si="20"/>
@@ -11672,7 +11578,7 @@
       </c>
       <c r="CE24" s="13">
         <f t="shared" si="20"/>
-        <v>0.11999999999999998</v>
+        <v>7.8749999999999987E-2</v>
       </c>
       <c r="CF24" s="13">
         <f t="shared" si="20"/>
@@ -11680,7 +11586,7 @@
       </c>
       <c r="CG24" s="13">
         <f t="shared" si="20"/>
-        <v>4.6666666666666683E-2</v>
+        <v>4.3750000000000018E-2</v>
       </c>
     </row>
     <row r="25" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11735,17 +11641,17 @@
       <c r="R25" s="23">
         <v>1</v>
       </c>
-      <c r="T25" s="112"/>
-      <c r="U25" s="109"/>
-      <c r="V25" s="109"/>
-      <c r="W25" s="109"/>
-      <c r="X25" s="109"/>
-      <c r="Y25" s="109"/>
-      <c r="Z25" s="109"/>
-      <c r="AA25" s="109"/>
-      <c r="AB25" s="109"/>
-      <c r="AC25" s="109"/>
-      <c r="AD25" s="110"/>
+      <c r="T25" s="115"/>
+      <c r="U25" s="114"/>
+      <c r="V25" s="114"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="114"/>
+      <c r="Y25" s="114"/>
+      <c r="Z25" s="114"/>
+      <c r="AA25" s="114"/>
+      <c r="AB25" s="114"/>
+      <c r="AC25" s="114"/>
+      <c r="AD25" s="123"/>
       <c r="AL25" s="39" t="s">
         <v>8</v>
       </c>
@@ -11761,7 +11667,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP25" s="80">
+      <c r="AP25" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11837,22 +11743,22 @@
       <c r="BM25" s="45"/>
       <c r="BN25" s="45"/>
       <c r="BO25" s="30"/>
-      <c r="BP25" s="134" t="s">
+      <c r="BP25" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="BQ25" s="135"/>
-      <c r="BR25" s="134" t="s">
+      <c r="BQ25" s="132"/>
+      <c r="BR25" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="BS25" s="135"/>
-      <c r="BT25" s="134" t="s">
+      <c r="BS25" s="132"/>
+      <c r="BT25" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="BU25" s="135"/>
-      <c r="BV25" s="134" t="s">
+      <c r="BU25" s="132"/>
+      <c r="BV25" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="BW25" s="135"/>
+      <c r="BW25" s="132"/>
       <c r="BY25" s="4" t="s">
         <v>4</v>
       </c>
@@ -11862,15 +11768,15 @@
       </c>
       <c r="CA25" s="13">
         <f t="shared" si="20"/>
-        <v>5.8193277310924378E-2</v>
+        <v>5.9090909090909097E-2</v>
       </c>
       <c r="CB25" s="13">
         <f t="shared" si="20"/>
-        <v>5.7983193277310927E-2</v>
+        <v>9.8701298701298706E-2</v>
       </c>
       <c r="CC25" s="13">
         <f t="shared" si="20"/>
-        <v>0.26491596638655462</v>
+        <v>0.23636363636363639</v>
       </c>
       <c r="CD25" s="13">
         <f t="shared" si="20"/>
@@ -11878,7 +11784,7 @@
       </c>
       <c r="CE25" s="13">
         <f t="shared" si="20"/>
-        <v>0.10909090909090909</v>
+        <v>7.159090909090908E-2</v>
       </c>
       <c r="CF25" s="13">
         <f t="shared" si="20"/>
@@ -11886,7 +11792,7 @@
       </c>
       <c r="CG25" s="13">
         <f t="shared" si="20"/>
-        <v>8.484848484848484E-2</v>
+        <v>7.9545454545454544E-2</v>
       </c>
     </row>
     <row r="26" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11941,19 +11847,19 @@
       <c r="R26" s="23">
         <v>0</v>
       </c>
-      <c r="T26" s="112" t="s">
+      <c r="T26" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="U26" s="109"/>
-      <c r="V26" s="109"/>
-      <c r="W26" s="109"/>
-      <c r="X26" s="109"/>
-      <c r="Y26" s="109"/>
-      <c r="Z26" s="109"/>
-      <c r="AA26" s="109"/>
-      <c r="AB26" s="109"/>
-      <c r="AC26" s="109"/>
-      <c r="AD26" s="110"/>
+      <c r="U26" s="114"/>
+      <c r="V26" s="114"/>
+      <c r="W26" s="114"/>
+      <c r="X26" s="114"/>
+      <c r="Y26" s="114"/>
+      <c r="Z26" s="114"/>
+      <c r="AA26" s="114"/>
+      <c r="AB26" s="114"/>
+      <c r="AC26" s="114"/>
+      <c r="AD26" s="123"/>
       <c r="AL26" s="39" t="s">
         <v>9</v>
       </c>
@@ -11969,7 +11875,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP26" s="80">
+      <c r="AP26" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -12078,15 +11984,15 @@
       </c>
       <c r="CA26" s="13">
         <f t="shared" si="20"/>
-        <v>5.8193277310924378E-2</v>
+        <v>5.9090909090909097E-2</v>
       </c>
       <c r="CB26" s="13">
         <f t="shared" si="20"/>
-        <v>5.7983193277310927E-2</v>
+        <v>9.8701298701298706E-2</v>
       </c>
       <c r="CC26" s="13">
         <f t="shared" si="20"/>
-        <v>0.26491596638655462</v>
+        <v>0.23636363636363639</v>
       </c>
       <c r="CD26" s="13">
         <f t="shared" si="20"/>
@@ -12094,7 +12000,7 @@
       </c>
       <c r="CE26" s="13">
         <f t="shared" si="20"/>
-        <v>0.10909090909090909</v>
+        <v>7.159090909090908E-2</v>
       </c>
       <c r="CF26" s="13">
         <f t="shared" si="20"/>
@@ -12102,7 +12008,7 @@
       </c>
       <c r="CG26" s="13">
         <f t="shared" si="20"/>
-        <v>8.484848484848484E-2</v>
+        <v>7.9545454545454544E-2</v>
       </c>
     </row>
     <row r="27" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12157,31 +12063,31 @@
       <c r="R27" s="23">
         <v>2</v>
       </c>
-      <c r="T27" s="112" t="s">
+      <c r="T27" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="U27" s="109">
+      <c r="U27" s="114">
         <f>MAX(U4:U8)</f>
         <v>9</v>
       </c>
-      <c r="V27" s="109">
+      <c r="V27" s="114">
         <f>MAX(V16:V19)</f>
         <v>96</v>
       </c>
-      <c r="W27" s="109">
+      <c r="W27" s="114">
         <f>MAX(W18:W19)</f>
         <v>26</v>
       </c>
-      <c r="X27" s="109">
+      <c r="X27" s="114">
         <f>MAX(X4:X13)</f>
         <v>1</v>
       </c>
-      <c r="Y27" s="109"/>
-      <c r="Z27" s="109"/>
-      <c r="AA27" s="109"/>
-      <c r="AB27" s="109"/>
-      <c r="AC27" s="109"/>
-      <c r="AD27" s="110"/>
+      <c r="Y27" s="114"/>
+      <c r="Z27" s="114"/>
+      <c r="AA27" s="114"/>
+      <c r="AB27" s="114"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="123"/>
       <c r="AL27" s="39" t="s">
         <v>10</v>
       </c>
@@ -12197,7 +12103,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP27" s="80">
+      <c r="AP27" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -12308,15 +12214,15 @@
       </c>
       <c r="CA27" s="13">
         <f t="shared" si="20"/>
-        <v>8.4279918864097358E-2</v>
+        <v>8.5579937304075232E-2</v>
       </c>
       <c r="CB27" s="13">
         <f t="shared" si="20"/>
-        <v>5.3651115618661246E-2</v>
+        <v>9.1327063740856834E-2</v>
       </c>
       <c r="CC27" s="13">
         <f t="shared" si="20"/>
-        <v>0.2557809330628803</v>
+        <v>0.22821316614420065</v>
       </c>
       <c r="CD27" s="13">
         <f t="shared" si="20"/>
@@ -12324,7 +12230,7 @@
       </c>
       <c r="CE27" s="13">
         <f t="shared" si="20"/>
-        <v>0.10909090909090909</v>
+        <v>7.159090909090908E-2</v>
       </c>
       <c r="CF27" s="13">
         <f t="shared" si="20"/>
@@ -12332,7 +12238,7 @@
       </c>
       <c r="CG27" s="13">
         <f t="shared" si="20"/>
-        <v>8.484848484848484E-2</v>
+        <v>7.9545454545454544E-2</v>
       </c>
     </row>
     <row r="28" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12387,31 +12293,31 @@
       <c r="R28" s="23">
         <v>0</v>
       </c>
-      <c r="T28" s="112" t="s">
-        <v>37</v>
-      </c>
-      <c r="U28" s="109">
+      <c r="T28" s="115" t="s">
+        <v>107</v>
+      </c>
+      <c r="U28" s="114">
         <f>MAX(U9:U14)</f>
         <v>28</v>
       </c>
-      <c r="V28" s="109">
+      <c r="V28" s="114">
         <f>MAX(V9:V15)</f>
         <v>66</v>
       </c>
-      <c r="W28" s="109">
+      <c r="W28" s="114">
         <f>MAX(W16:W17)</f>
         <v>8</v>
       </c>
-      <c r="X28" s="109">
+      <c r="X28" s="114">
         <f>MAX(X14:X15)</f>
         <v>5</v>
       </c>
-      <c r="Y28" s="109"/>
-      <c r="Z28" s="109"/>
-      <c r="AA28" s="109"/>
-      <c r="AB28" s="109"/>
-      <c r="AC28" s="109"/>
-      <c r="AD28" s="110"/>
+      <c r="Y28" s="114"/>
+      <c r="Z28" s="114"/>
+      <c r="AA28" s="114"/>
+      <c r="AB28" s="114"/>
+      <c r="AC28" s="114"/>
+      <c r="AD28" s="123"/>
       <c r="AL28" s="39" t="s">
         <v>11</v>
       </c>
@@ -12427,7 +12333,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP28" s="80">
+      <c r="AP28" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -12538,15 +12444,15 @@
       </c>
       <c r="CA28" s="13">
         <f t="shared" si="20"/>
-        <v>5.8193277310924378E-2</v>
+        <v>5.9090909090909097E-2</v>
       </c>
       <c r="CB28" s="13">
         <f t="shared" si="20"/>
-        <v>5.7983193277310927E-2</v>
+        <v>9.8701298701298706E-2</v>
       </c>
       <c r="CC28" s="13">
         <f t="shared" si="20"/>
-        <v>0.26491596638655462</v>
+        <v>0.23636363636363639</v>
       </c>
       <c r="CD28" s="13">
         <f t="shared" si="20"/>
@@ -12554,7 +12460,7 @@
       </c>
       <c r="CE28" s="13">
         <f t="shared" si="20"/>
-        <v>9.9999999999999978E-2</v>
+        <v>6.5624999999999989E-2</v>
       </c>
       <c r="CF28" s="13">
         <f t="shared" si="20"/>
@@ -12562,7 +12468,7 @@
       </c>
       <c r="CG28" s="13">
         <f t="shared" si="20"/>
-        <v>0.11666666666666667</v>
+        <v>0.10937500000000001</v>
       </c>
     </row>
     <row r="29" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12617,31 +12523,31 @@
       <c r="R29" s="23">
         <v>0</v>
       </c>
-      <c r="T29" s="112" t="s">
-        <v>107</v>
-      </c>
-      <c r="U29" s="109">
+      <c r="T29" s="115" t="s">
+        <v>37</v>
+      </c>
+      <c r="U29" s="114">
         <f>MAX(U15:U19)</f>
         <v>116</v>
       </c>
-      <c r="V29" s="109">
+      <c r="V29" s="114">
         <f>MAX(V4:V8)</f>
         <v>38</v>
       </c>
-      <c r="W29" s="109">
+      <c r="W29" s="114">
         <f>MAX(W4:W15)</f>
         <v>3</v>
       </c>
-      <c r="X29" s="109">
+      <c r="X29" s="114">
         <f>MAX(X16:X19)</f>
         <v>9</v>
       </c>
-      <c r="Y29" s="109"/>
-      <c r="Z29" s="109"/>
-      <c r="AA29" s="109"/>
-      <c r="AB29" s="109"/>
-      <c r="AC29" s="109"/>
-      <c r="AD29" s="110"/>
+      <c r="Y29" s="114"/>
+      <c r="Z29" s="114"/>
+      <c r="AA29" s="114"/>
+      <c r="AB29" s="114"/>
+      <c r="AC29" s="114"/>
+      <c r="AD29" s="123"/>
       <c r="AL29" s="39" t="s">
         <v>12</v>
       </c>
@@ -12657,7 +12563,7 @@
         <f t="shared" si="2"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="AP29" s="80">
+      <c r="AP29" s="79">
         <f t="shared" si="3"/>
         <v>0.22222222222222221</v>
       </c>
@@ -12768,15 +12674,15 @@
       </c>
       <c r="CA29" s="13">
         <f t="shared" si="20"/>
-        <v>8.4279918864097358E-2</v>
+        <v>8.5579937304075232E-2</v>
       </c>
       <c r="CB29" s="13">
         <f t="shared" si="20"/>
-        <v>5.3651115618661246E-2</v>
+        <v>9.1327063740856834E-2</v>
       </c>
       <c r="CC29" s="13">
         <f t="shared" si="20"/>
-        <v>0.2557809330628803</v>
+        <v>0.22821316614420065</v>
       </c>
       <c r="CD29" s="13">
         <f t="shared" si="20"/>
@@ -12784,7 +12690,7 @@
       </c>
       <c r="CE29" s="13">
         <f t="shared" si="20"/>
-        <v>6.6666666666666666E-2</v>
+        <v>4.3749999999999997E-2</v>
       </c>
       <c r="CF29" s="13">
         <f t="shared" si="20"/>
@@ -12792,7 +12698,7 @@
       </c>
       <c r="CG29" s="13">
         <f t="shared" si="20"/>
-        <v>0.23333333333333334</v>
+        <v>0.21875000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12847,17 +12753,17 @@
       <c r="R30" s="23">
         <v>0</v>
       </c>
-      <c r="T30" s="112"/>
-      <c r="U30" s="109"/>
-      <c r="V30" s="109"/>
-      <c r="W30" s="109"/>
-      <c r="X30" s="109"/>
-      <c r="Y30" s="109"/>
-      <c r="Z30" s="109"/>
-      <c r="AA30" s="109"/>
-      <c r="AB30" s="109"/>
-      <c r="AC30" s="109"/>
-      <c r="AD30" s="110"/>
+      <c r="T30" s="115"/>
+      <c r="U30" s="114"/>
+      <c r="V30" s="114"/>
+      <c r="W30" s="114"/>
+      <c r="X30" s="114"/>
+      <c r="Y30" s="114"/>
+      <c r="Z30" s="114"/>
+      <c r="AA30" s="114"/>
+      <c r="AB30" s="114"/>
+      <c r="AC30" s="114"/>
+      <c r="AD30" s="123"/>
       <c r="AL30" s="39" t="s">
         <v>13</v>
       </c>
@@ -12873,7 +12779,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP30" s="80">
+      <c r="AP30" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -12980,19 +12886,19 @@
       </c>
       <c r="BZ30" s="13">
         <f t="shared" si="20"/>
-        <v>1.1505190311418684E-2</v>
+        <v>1.2700534759358287E-2</v>
       </c>
       <c r="CA30" s="13">
         <f t="shared" si="20"/>
-        <v>0.21565743944636678</v>
+        <v>0.21898395721925135</v>
       </c>
       <c r="CB30" s="13">
         <f t="shared" si="20"/>
-        <v>3.3823529411764704E-2</v>
+        <v>5.7575757575757572E-2</v>
       </c>
       <c r="CC30" s="13">
         <f t="shared" si="20"/>
-        <v>0.20977508650519031</v>
+        <v>0.18716577540106955</v>
       </c>
       <c r="CD30" s="13">
         <f t="shared" si="20"/>
@@ -13000,15 +12906,15 @@
       </c>
       <c r="CE30" s="13">
         <f t="shared" si="20"/>
-        <v>7.179487179487179E-2</v>
+        <v>4.7115384615384608E-2</v>
       </c>
       <c r="CF30" s="13">
         <f t="shared" si="20"/>
-        <v>1.7948717948717944E-2</v>
+        <v>2.4358974358974356E-2</v>
       </c>
       <c r="CG30" s="13">
         <f t="shared" si="20"/>
-        <v>0.21538461538461542</v>
+        <v>0.20192307692307698</v>
       </c>
     </row>
     <row r="31" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13063,19 +12969,19 @@
       <c r="R31" s="23">
         <v>0</v>
       </c>
-      <c r="T31" s="112" t="s">
+      <c r="T31" s="115" t="s">
         <v>117</v>
       </c>
-      <c r="U31" s="109"/>
-      <c r="V31" s="109"/>
-      <c r="W31" s="109"/>
-      <c r="X31" s="109"/>
-      <c r="Y31" s="109"/>
-      <c r="Z31" s="109"/>
-      <c r="AA31" s="109"/>
-      <c r="AB31" s="109"/>
-      <c r="AC31" s="109"/>
-      <c r="AD31" s="110"/>
+      <c r="U31" s="114"/>
+      <c r="V31" s="114"/>
+      <c r="W31" s="114"/>
+      <c r="X31" s="114"/>
+      <c r="Y31" s="114"/>
+      <c r="Z31" s="114"/>
+      <c r="AA31" s="114"/>
+      <c r="AB31" s="114"/>
+      <c r="AC31" s="114"/>
+      <c r="AD31" s="123"/>
       <c r="AL31" s="39" t="s">
         <v>14</v>
       </c>
@@ -13091,7 +12997,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP31" s="80">
+      <c r="AP31" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -13206,11 +13112,11 @@
       </c>
       <c r="CB31" s="13">
         <f t="shared" si="20"/>
-        <v>6.7647058823529407E-2</v>
+        <v>0.11515151515151514</v>
       </c>
       <c r="CC31" s="13">
         <f t="shared" si="20"/>
-        <v>0.28529411764705881</v>
+        <v>0.25454545454545457</v>
       </c>
       <c r="CD31" s="13">
         <f t="shared" si="20"/>
@@ -13218,7 +13124,7 @@
       </c>
       <c r="CE31" s="13">
         <f t="shared" si="20"/>
-        <v>0.13333333333333333</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="CF31" s="13">
         <f t="shared" si="20"/>
@@ -13281,29 +13187,29 @@
       <c r="R32" s="23">
         <v>2</v>
       </c>
-      <c r="T32" s="112"/>
-      <c r="U32" s="109">
-        <f>(U27+U28+U24)</f>
-        <v>88</v>
-      </c>
-      <c r="V32" s="109">
-        <f t="shared" ref="V32:X32" si="21">(V27+V28+V24)</f>
-        <v>176</v>
-      </c>
-      <c r="W32" s="109">
+      <c r="T32" s="115"/>
+      <c r="U32" s="114">
+        <f>(U27+U29+U23)</f>
+        <v>135</v>
+      </c>
+      <c r="V32" s="114">
+        <f t="shared" ref="V32:X32" si="21">(V27+V29+V23)</f>
+        <v>174</v>
+      </c>
+      <c r="W32" s="114">
         <f t="shared" si="21"/>
-        <v>34</v>
-      </c>
-      <c r="X32" s="109">
+        <v>33</v>
+      </c>
+      <c r="X32" s="114">
         <f t="shared" si="21"/>
         <v>12</v>
       </c>
-      <c r="Y32" s="119"/>
-      <c r="Z32" s="120"/>
-      <c r="AA32" s="120"/>
-      <c r="AB32" s="120"/>
-      <c r="AC32" s="120"/>
-      <c r="AD32" s="121"/>
+      <c r="Y32" s="91"/>
+      <c r="Z32" s="92"/>
+      <c r="AA32" s="92"/>
+      <c r="AB32" s="92"/>
+      <c r="AC32" s="92"/>
+      <c r="AD32" s="93"/>
       <c r="AL32" s="39" t="s">
         <v>15</v>
       </c>
@@ -13319,7 +13225,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP32" s="80">
+      <c r="AP32" s="79">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -13426,19 +13332,19 @@
       </c>
       <c r="BZ32" s="13">
         <f t="shared" si="20"/>
-        <v>9.5408895265423239E-3</v>
+        <v>1.0532150776053214E-2</v>
       </c>
       <c r="CA32" s="13">
         <f t="shared" si="20"/>
-        <v>0.31793400286944046</v>
+        <v>0.32283813747228385</v>
       </c>
       <c r="CB32" s="13">
         <f t="shared" si="20"/>
-        <v>1.6499282639885222E-2</v>
+        <v>2.8085735402808572E-2</v>
       </c>
       <c r="CC32" s="13">
         <f t="shared" si="20"/>
-        <v>0.17395982783357244</v>
+        <v>0.15521064301552107</v>
       </c>
       <c r="CD32" s="13">
         <f t="shared" si="20"/>
@@ -13446,7 +13352,7 @@
       </c>
       <c r="CE32" s="13">
         <f t="shared" si="20"/>
-        <v>7.4999999999999997E-2</v>
+        <v>4.9218749999999999E-2</v>
       </c>
       <c r="CF32" s="13">
         <f t="shared" si="20"/>
@@ -13454,7 +13360,7 @@
       </c>
       <c r="CG32" s="13">
         <f t="shared" si="20"/>
-        <v>0.20416666666666669</v>
+        <v>0.19140625000000006</v>
       </c>
     </row>
     <row r="33" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13509,19 +13415,16 @@
       <c r="R33" s="23">
         <v>4</v>
       </c>
-      <c r="T33" s="112"/>
-      <c r="U33" s="109"/>
-      <c r="V33" s="109"/>
-      <c r="W33" s="109"/>
-      <c r="X33" s="109"/>
-      <c r="Y33" s="122"/>
-      <c r="Z33" s="116" t="s">
+      <c r="T33" s="115"/>
+      <c r="U33" s="114"/>
+      <c r="V33" s="114"/>
+      <c r="W33" s="114"/>
+      <c r="X33" s="114"/>
+      <c r="Y33" s="94"/>
+      <c r="Z33" s="109" t="s">
         <v>133</v>
       </c>
-      <c r="AA33" s="117"/>
-      <c r="AB33" s="117"/>
-      <c r="AC33" s="117"/>
-      <c r="AD33" s="123"/>
+      <c r="AD33" s="95"/>
       <c r="AL33" s="39" t="s">
         <v>16</v>
       </c>
@@ -13537,7 +13440,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP33" s="80">
+      <c r="AP33" s="79">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -13648,15 +13551,15 @@
       </c>
       <c r="CA33" s="13">
         <f t="shared" si="20"/>
-        <v>8.4279918864097358E-2</v>
+        <v>8.5579937304075232E-2</v>
       </c>
       <c r="CB33" s="13">
         <f t="shared" si="20"/>
-        <v>5.3651115618661246E-2</v>
+        <v>9.1327063740856834E-2</v>
       </c>
       <c r="CC33" s="13">
         <f t="shared" si="20"/>
-        <v>0.2557809330628803</v>
+        <v>0.22821316614420065</v>
       </c>
       <c r="CD33" s="13">
         <f t="shared" si="20"/>
@@ -13664,7 +13567,7 @@
       </c>
       <c r="CE33" s="13">
         <f t="shared" si="20"/>
-        <v>8.5714285714285701E-2</v>
+        <v>5.6249999999999988E-2</v>
       </c>
       <c r="CF33" s="13">
         <f t="shared" si="20"/>
@@ -13672,7 +13575,7 @@
       </c>
       <c r="CG33" s="13">
         <f t="shared" si="20"/>
-        <v>0.16666666666666669</v>
+        <v>0.15625000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -13727,27 +13630,24 @@
       <c r="R34" s="23">
         <v>0</v>
       </c>
-      <c r="T34" s="112"/>
-      <c r="U34" s="113" t="s">
+      <c r="T34" s="115"/>
+      <c r="U34" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="V34" s="113" t="s">
+      <c r="V34" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="W34" s="113" t="s">
+      <c r="W34" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="X34" s="127" t="s">
+      <c r="X34" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="Y34" s="122"/>
-      <c r="Z34" s="117" t="s">
+      <c r="Y34" s="94"/>
+      <c r="Z34" t="s">
         <v>134</v>
       </c>
-      <c r="AA34" s="117"/>
-      <c r="AB34" s="117"/>
-      <c r="AC34" s="117"/>
-      <c r="AD34" s="123"/>
+      <c r="AD34" s="95"/>
       <c r="AL34" s="39" t="s">
         <v>17</v>
       </c>
@@ -13763,7 +13663,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP34" s="80">
+      <c r="AP34" s="79">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13874,15 +13774,15 @@
       </c>
       <c r="CA34" s="13">
         <f t="shared" si="20"/>
-        <v>3.0174291938997819E-2</v>
+        <v>3.0639730639730637E-2</v>
       </c>
       <c r="CB34" s="13">
         <f t="shared" si="20"/>
-        <v>6.2636165577342043E-2</v>
+        <v>0.10662177328843994</v>
       </c>
       <c r="CC34" s="13">
         <f t="shared" si="20"/>
-        <v>0.27472766884531585</v>
+        <v>0.24511784511784512</v>
       </c>
       <c r="CD34" s="13">
         <f t="shared" si="20"/>
@@ -13890,7 +13790,7 @@
       </c>
       <c r="CE34" s="13">
         <f t="shared" si="20"/>
-        <v>0.08</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="CF34" s="13">
         <f t="shared" si="20"/>
@@ -13898,26 +13798,26 @@
       </c>
       <c r="CG34" s="13">
         <f t="shared" si="20"/>
-        <v>0.18666666666666668</v>
+        <v>0.17500000000000004</v>
       </c>
     </row>
     <row r="35" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="75">
-        <v>0</v>
-      </c>
-      <c r="D35" s="75">
-        <v>0</v>
-      </c>
-      <c r="E35" s="75">
-        <v>0</v>
-      </c>
-      <c r="F35" s="76">
+      <c r="C35" s="74">
+        <v>0</v>
+      </c>
+      <c r="D35" s="74">
+        <v>0</v>
+      </c>
+      <c r="E35" s="74">
+        <v>0</v>
+      </c>
+      <c r="F35" s="75">
         <v>0</v>
       </c>
       <c r="H35" s="39" t="s">
@@ -13953,47 +13853,43 @@
       <c r="R35" s="23">
         <v>0</v>
       </c>
-      <c r="T35" s="15" t="s">
+      <c r="T35" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="U35" s="56">
+      <c r="U35" s="119">
         <f>U22/U$32</f>
-        <v>2.2727272727272728E-2</v>
-      </c>
-      <c r="V35" s="56">
+        <v>1.4814814814814815E-2</v>
+      </c>
+      <c r="V35" s="119">
         <f>V22/V$32</f>
-        <v>0.39772727272727271</v>
-      </c>
-      <c r="W35" s="56">
+        <v>0.40229885057471265</v>
+      </c>
+      <c r="W35" s="119">
         <f>W22/W$32</f>
-        <v>0.44117647058823528</v>
-      </c>
-      <c r="X35" s="56">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="X35" s="119">
         <f>X22/X$32</f>
         <v>0</v>
       </c>
-      <c r="Y35" s="122"/>
-      <c r="Z35" s="117"/>
-      <c r="AA35" s="117"/>
-      <c r="AB35" s="117"/>
-      <c r="AC35" s="117"/>
-      <c r="AD35" s="123"/>
+      <c r="Y35" s="94"/>
+      <c r="AD35" s="95"/>
       <c r="AL35" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="AM35" s="81">
+      <c r="AM35" s="80">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN35" s="82">
+      <c r="AN35" s="81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO35" s="82">
+      <c r="AO35" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="83">
+      <c r="AP35" s="82">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -14104,15 +14000,15 @@
       </c>
       <c r="CA35" s="13">
         <f t="shared" si="20"/>
-        <v>8.4279918864097358E-2</v>
+        <v>8.5579937304075232E-2</v>
       </c>
       <c r="CB35" s="13">
         <f t="shared" si="20"/>
-        <v>5.3651115618661246E-2</v>
+        <v>9.1327063740856834E-2</v>
       </c>
       <c r="CC35" s="13">
         <f t="shared" si="20"/>
-        <v>0.2557809330628803</v>
+        <v>0.22821316614420065</v>
       </c>
       <c r="CD35" s="13">
         <f t="shared" si="20"/>
@@ -14120,7 +14016,7 @@
       </c>
       <c r="CE35" s="13">
         <f t="shared" si="20"/>
-        <v>0.10909090909090909</v>
+        <v>7.159090909090908E-2</v>
       </c>
       <c r="CF35" s="13">
         <f t="shared" si="20"/>
@@ -14128,26 +14024,26 @@
       </c>
       <c r="CG35" s="13">
         <f t="shared" si="20"/>
-        <v>8.484848484848484E-2</v>
+        <v>7.9545454545454544E-2</v>
       </c>
     </row>
     <row r="36" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="71">
+      <c r="B36" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="70">
         <v>144</v>
       </c>
-      <c r="D36" s="71">
+      <c r="D36" s="70">
         <v>51</v>
       </c>
-      <c r="E36" s="71">
+      <c r="E36" s="70">
         <v>6</v>
       </c>
-      <c r="F36" s="72">
+      <c r="F36" s="71">
         <v>2</v>
       </c>
       <c r="H36" s="39" t="s">
@@ -14183,24 +14079,24 @@
       <c r="R36" s="23">
         <v>1</v>
       </c>
-      <c r="T36" s="16"/>
-      <c r="U36" s="37">
+      <c r="T36" s="115"/>
+      <c r="U36" s="120">
         <f>U27/U$32</f>
-        <v>0.10227272727272728</v>
-      </c>
-      <c r="V36" s="37">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="V36" s="120">
         <f>V27/V$32</f>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="W36" s="37">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="W36" s="120">
         <f>W27/W$32</f>
-        <v>0.76470588235294112</v>
-      </c>
-      <c r="X36" s="118">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="X36" s="120">
         <f>X27/X$32</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="Y36" s="122"/>
+      <c r="Y36" s="94"/>
       <c r="Z36" s="16"/>
       <c r="AA36" s="7" t="s">
         <v>64</v>
@@ -14211,25 +14107,25 @@
       <c r="AC36" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="AD36" s="128" t="s">
+      <c r="AD36" s="99" t="s">
         <v>67</v>
       </c>
       <c r="AL36" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM36" s="87">
+      <c r="AM36" s="86">
         <f t="shared" ref="AM36:AM67" si="22">(AG$4-C36)/(AG$4-AG$5)</f>
         <v>0.53697749196141475</v>
       </c>
-      <c r="AN36" s="88">
+      <c r="AN36" s="87">
         <f t="shared" ref="AN36:AN67" si="23">(D36-AH$5)/(AH$4-AH$5)</f>
         <v>0.28813559322033899</v>
       </c>
-      <c r="AO36" s="88">
+      <c r="AO36" s="87">
         <f t="shared" ref="AO36:AO67" si="24">(E36-AI$5)/(AI$4-AI$5)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP36" s="89">
+      <c r="AP36" s="88">
         <f t="shared" ref="AP36:AP67" si="25">(AJ$4-F36)/(AJ$4-AJ$5)</f>
         <v>0.77777777777777779</v>
       </c>
@@ -14336,19 +14232,19 @@
       </c>
       <c r="BZ36" s="13">
         <f t="shared" si="20"/>
-        <v>9.7794117647058837E-3</v>
+        <v>1.0795454545454546E-2</v>
       </c>
       <c r="CA36" s="13">
         <f t="shared" si="20"/>
-        <v>0.30551470588235297</v>
+        <v>0.31022727272727274</v>
       </c>
       <c r="CB36" s="13">
         <f t="shared" si="20"/>
-        <v>1.8602941176470593E-2</v>
+        <v>3.1666666666666676E-2</v>
       </c>
       <c r="CC36" s="13">
         <f t="shared" si="20"/>
-        <v>0.1783088235294118</v>
+        <v>0.15909090909090914</v>
       </c>
       <c r="CD36" s="13">
         <f t="shared" si="20"/>
@@ -14356,15 +14252,15 @@
       </c>
       <c r="CE36" s="13">
         <f t="shared" si="20"/>
-        <v>5.8333333333333341E-2</v>
+        <v>3.8281250000000003E-2</v>
       </c>
       <c r="CF36" s="13">
         <f t="shared" si="20"/>
-        <v>1.4583333333333332E-2</v>
+        <v>1.9791666666666666E-2</v>
       </c>
       <c r="CG36" s="13">
         <f t="shared" si="20"/>
-        <v>0.26250000000000001</v>
+        <v>0.24609375000000003</v>
       </c>
     </row>
     <row r="37" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14419,43 +14315,43 @@
       <c r="R37" s="23">
         <v>0</v>
       </c>
-      <c r="T37" s="16" t="s">
+      <c r="T37" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="U37" s="37">
+      <c r="U37" s="120">
         <f>U23/U$32</f>
-        <v>0.11363636363636363</v>
-      </c>
-      <c r="V37" s="37">
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="V37" s="120">
         <f>V23/V$32</f>
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="W37" s="37">
+        <v>0.22988505747126436</v>
+      </c>
+      <c r="W37" s="120">
         <f>W23/W$32</f>
-        <v>0.11764705882352941</v>
-      </c>
-      <c r="X37" s="118">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="X37" s="120">
         <f>X23/X$32</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="Y37" s="122"/>
+      <c r="Y37" s="94"/>
       <c r="Z37" s="15" t="s">
         <v>38</v>
       </c>
       <c r="AA37" s="56">
-        <f>MAX(0,U35-5%)</f>
-        <v>0</v>
+        <f>MAX(0,U35*0.95)</f>
+        <v>1.4074074074074074E-2</v>
       </c>
       <c r="AB37" s="56">
-        <f>MAX(0,V35-5%)</f>
-        <v>0.34772727272727272</v>
+        <f t="shared" ref="AB37:AD37" si="26">MAX(0,V35*0.95)</f>
+        <v>0.38218390804597702</v>
       </c>
       <c r="AC37" s="56">
-        <f>MAX(0,W35-5%)</f>
-        <v>0.39117647058823529</v>
-      </c>
-      <c r="AD37" s="129">
-        <f>MAX(0,X35-5%)</f>
+        <f t="shared" si="26"/>
+        <v>0.43181818181818177</v>
+      </c>
+      <c r="AD37" s="100">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AL37" s="39" t="s">
@@ -14473,7 +14369,7 @@
         <f t="shared" si="24"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP37" s="80">
+      <c r="AP37" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -14584,15 +14480,15 @@
       </c>
       <c r="CA37" s="13">
         <f t="shared" si="20"/>
-        <v>3.0174291938997819E-2</v>
+        <v>3.0639730639730637E-2</v>
       </c>
       <c r="CB37" s="13">
         <f t="shared" si="20"/>
-        <v>6.2636165577342043E-2</v>
+        <v>0.10662177328843994</v>
       </c>
       <c r="CC37" s="13">
         <f t="shared" si="20"/>
-        <v>0.27472766884531585</v>
+        <v>0.24511784511784512</v>
       </c>
       <c r="CD37" s="13">
         <f t="shared" si="20"/>
@@ -14600,7 +14496,7 @@
       </c>
       <c r="CE37" s="13">
         <f t="shared" si="20"/>
-        <v>0.10909090909090909</v>
+        <v>7.159090909090908E-2</v>
       </c>
       <c r="CF37" s="13">
         <f t="shared" si="20"/>
@@ -14608,7 +14504,7 @@
       </c>
       <c r="CG37" s="13">
         <f t="shared" si="20"/>
-        <v>8.484848484848484E-2</v>
+        <v>7.9545454545454544E-2</v>
       </c>
     </row>
     <row r="38" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14663,40 +14559,40 @@
       <c r="R38" s="23">
         <v>2</v>
       </c>
-      <c r="T38" s="17"/>
-      <c r="U38" s="57">
+      <c r="T38" s="115"/>
+      <c r="U38" s="141">
         <f>U28/U$32</f>
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="V38" s="57">
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="V38" s="141">
         <f>V28/V$32</f>
-        <v>0.375</v>
-      </c>
-      <c r="W38" s="57">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="W38" s="141">
         <f>W28/W$32</f>
-        <v>0.23529411764705882</v>
-      </c>
-      <c r="X38" s="57">
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="X38" s="141">
         <f>X28/X$32</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="Y38" s="122"/>
+      <c r="Y38" s="94"/>
       <c r="Z38" s="16"/>
-      <c r="AA38" s="118">
-        <f>MIN(1,U36+5%)</f>
-        <v>0.15227272727272728</v>
-      </c>
-      <c r="AB38" s="118">
-        <f>MIN(1,V36+5%)</f>
-        <v>0.59545454545454546</v>
-      </c>
-      <c r="AC38" s="118">
-        <f>MIN(1,W36+5%)</f>
-        <v>0.81470588235294117</v>
-      </c>
-      <c r="AD38" s="130">
-        <f>MIN(1,X36+5%)</f>
-        <v>0.13333333333333333</v>
+      <c r="AA38" s="37">
+        <f>MIN(1,U36*1.05)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AB38" s="37">
+        <f t="shared" ref="AB38:AD38" si="27">MIN(1,V36*1.05)</f>
+        <v>0.57931034482758625</v>
+      </c>
+      <c r="AC38" s="37">
+        <f t="shared" si="27"/>
+        <v>0.82727272727272727</v>
+      </c>
+      <c r="AD38" s="101">
+        <f t="shared" si="27"/>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="AL38" s="39" t="s">
         <v>4</v>
@@ -14713,7 +14609,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP38" s="80">
+      <c r="AP38" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -14824,15 +14720,15 @@
       </c>
       <c r="CA38" s="13">
         <f t="shared" si="20"/>
-        <v>0.1916955017301038</v>
+        <v>0.19465240641711229</v>
       </c>
       <c r="CB38" s="13">
         <f t="shared" si="20"/>
-        <v>3.5813148788927336E-2</v>
+        <v>6.0962566844919783E-2</v>
       </c>
       <c r="CC38" s="13">
         <f t="shared" si="20"/>
-        <v>0.21816608996539791</v>
+        <v>0.19465240641711232</v>
       </c>
       <c r="CD38" s="13">
         <f t="shared" si="20"/>
@@ -14840,7 +14736,7 @@
       </c>
       <c r="CE38" s="13">
         <f t="shared" si="20"/>
-        <v>0.11999999999999998</v>
+        <v>7.8749999999999987E-2</v>
       </c>
       <c r="CF38" s="13">
         <f t="shared" si="20"/>
@@ -14848,7 +14744,7 @@
       </c>
       <c r="CG38" s="13">
         <f t="shared" si="20"/>
-        <v>4.6666666666666683E-2</v>
+        <v>4.3750000000000018E-2</v>
       </c>
     </row>
     <row r="39" spans="1:85" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14903,28 +14799,32 @@
       <c r="R39" s="23">
         <v>0</v>
       </c>
-      <c r="T39" s="16" t="s">
+      <c r="T39" s="91" t="s">
         <v>121</v>
       </c>
-      <c r="Y39" s="122"/>
+      <c r="U39" s="92"/>
+      <c r="V39" s="92"/>
+      <c r="W39" s="92"/>
+      <c r="X39" s="93"/>
+      <c r="Y39" s="94"/>
       <c r="Z39" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AA39" s="118">
-        <f>MAX(0,U37-5%)</f>
-        <v>6.363636363636363E-2</v>
-      </c>
-      <c r="AB39" s="118">
-        <f>MAX(0,V37-5%)</f>
-        <v>0.17727272727272725</v>
-      </c>
-      <c r="AC39" s="118">
-        <f>MAX(0,W37-5%)</f>
-        <v>6.7647058823529407E-2</v>
-      </c>
-      <c r="AD39" s="130">
-        <f>MAX(0,X37-5%)</f>
-        <v>0.11666666666666665</v>
+      <c r="AA39" s="37">
+        <f>MAX(0,U37*0.95)</f>
+        <v>7.0370370370370361E-2</v>
+      </c>
+      <c r="AB39" s="37">
+        <f t="shared" ref="AB39" si="28">MAX(0,V37*0.95)</f>
+        <v>0.21839080459770113</v>
+      </c>
+      <c r="AC39" s="37">
+        <f t="shared" ref="AC39" si="29">MAX(0,W37*0.95)</f>
+        <v>0.11515151515151514</v>
+      </c>
+      <c r="AD39" s="101">
+        <f t="shared" ref="AD39" si="30">MAX(0,X37*0.95)</f>
+        <v>0.15833333333333333</v>
       </c>
       <c r="AL39" s="39" t="s">
         <v>5</v>
@@ -14941,7 +14841,7 @@
         <f t="shared" si="24"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP39" s="80">
+      <c r="AP39" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -14979,21 +14879,21 @@
         <v>0</v>
       </c>
       <c r="BC39" s="45"/>
-      <c r="BD39" s="99" t="s">
+      <c r="BD39" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="BE39" s="101" t="s">
+      <c r="BE39" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="BF39" s="101"/>
-      <c r="BG39" s="101"/>
-      <c r="BH39" s="101"/>
-      <c r="BI39" s="101" t="s">
+      <c r="BF39" s="128"/>
+      <c r="BG39" s="128"/>
+      <c r="BH39" s="128"/>
+      <c r="BI39" s="128" t="s">
         <v>112</v>
       </c>
-      <c r="BJ39" s="101"/>
-      <c r="BK39" s="101"/>
-      <c r="BL39" s="102"/>
+      <c r="BJ39" s="128"/>
+      <c r="BK39" s="128"/>
+      <c r="BL39" s="129"/>
       <c r="BM39" s="45"/>
       <c r="BN39" s="45"/>
       <c r="BO39" s="4" t="s">
@@ -15076,40 +14976,40 @@
       <c r="R40" s="23">
         <v>0</v>
       </c>
-      <c r="T40" s="16"/>
-      <c r="U40" s="13">
-        <f>1+(U35+U36)/2-(U37+U38)/2</f>
-        <v>0.84659090909090906</v>
-      </c>
-      <c r="V40" s="13">
-        <f>1+(V35+V36)/2-(V37+V38)/2</f>
-        <v>1.1704545454545454</v>
-      </c>
-      <c r="W40" s="13">
-        <f>1+(W35+W36)/2-(W37+W38)/2</f>
-        <v>1.4264705882352942</v>
-      </c>
-      <c r="X40" s="13">
-        <f>1+(X35+X36)/2-(X37+X38)/2</f>
-        <v>0.75</v>
-      </c>
-      <c r="Y40" s="122"/>
+      <c r="T40" s="94"/>
+      <c r="U40" s="142">
+        <f>1+(AA37+AA38)/2-(AA39+AA40)/2</f>
+        <v>0.89796296296296307</v>
+      </c>
+      <c r="V40" s="142">
+        <f t="shared" ref="V40:X40" si="31">1+(AB37+AB38)/2-(AB39+AB40)/2</f>
+        <v>1.1724137931034482</v>
+      </c>
+      <c r="W40" s="142">
+        <f t="shared" si="31"/>
+        <v>1.4446969696969696</v>
+      </c>
+      <c r="X40" s="143">
+        <f t="shared" si="31"/>
+        <v>0.74583333333333324</v>
+      </c>
+      <c r="Y40" s="94"/>
       <c r="Z40" s="17"/>
       <c r="AA40" s="57">
-        <f>MIN(1,U38+5%)</f>
-        <v>0.36818181818181817</v>
+        <f>MIN(1,U38*1.05)</f>
+        <v>0.21777777777777779</v>
       </c>
       <c r="AB40" s="57">
-        <f>MIN(1,V38+5%)</f>
-        <v>0.42499999999999999</v>
+        <f t="shared" ref="AB40" si="32">MIN(1,V38*1.05)</f>
+        <v>0.39827586206896554</v>
       </c>
       <c r="AC40" s="57">
-        <f>MIN(1,W38+5%)</f>
-        <v>0.28529411764705881</v>
-      </c>
-      <c r="AD40" s="131">
-        <f>MIN(1,X38+5%)</f>
-        <v>0.46666666666666667</v>
+        <f t="shared" ref="AC40" si="33">MIN(1,W38*1.05)</f>
+        <v>0.25454545454545457</v>
+      </c>
+      <c r="AD40" s="102">
+        <f t="shared" ref="AD40" si="34">MIN(1,X38*1.05)</f>
+        <v>0.43750000000000006</v>
       </c>
       <c r="AL40" s="39" t="s">
         <v>6</v>
@@ -15126,7 +15026,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP40" s="80">
+      <c r="AP40" s="79">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -15164,7 +15064,7 @@
         <v>0</v>
       </c>
       <c r="BC40" s="45"/>
-      <c r="BD40" s="100"/>
+      <c r="BD40" s="127"/>
       <c r="BE40" s="47" t="s">
         <v>64</v>
       </c>
@@ -15271,20 +15171,20 @@
       <c r="R41" s="23">
         <v>1</v>
       </c>
-      <c r="T41" s="58">
+      <c r="T41" s="125">
         <f>SUM(U40:X40)/2</f>
-        <v>2.0967580213903743</v>
-      </c>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="124"/>
-      <c r="Z41" s="125"/>
-      <c r="AA41" s="125"/>
-      <c r="AB41" s="125"/>
-      <c r="AC41" s="125"/>
-      <c r="AD41" s="126"/>
+        <v>2.1304535295483573</v>
+      </c>
+      <c r="U41" s="97"/>
+      <c r="V41" s="97"/>
+      <c r="W41" s="97"/>
+      <c r="X41" s="98"/>
+      <c r="Y41" s="96"/>
+      <c r="Z41" s="97"/>
+      <c r="AA41" s="97"/>
+      <c r="AB41" s="97"/>
+      <c r="AC41" s="97"/>
+      <c r="AD41" s="98"/>
       <c r="AL41" s="39" t="s">
         <v>8</v>
       </c>
@@ -15300,7 +15200,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP41" s="80">
+      <c r="AP41" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -15342,35 +15242,35 @@
         <v>1</v>
       </c>
       <c r="BE41" s="13">
-        <f t="shared" ref="BE41:BH56" si="26">(1-BI5)/(BI5+1-BE5)</f>
+        <f t="shared" ref="BE41:BH56" si="35">(1-BI5)/(BI5+1-BE5)</f>
         <v>8.8691796008869041E-3</v>
       </c>
       <c r="BF41" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.27777777777777785</v>
       </c>
       <c r="BG41" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.64516129032258063</v>
       </c>
       <c r="BH41" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI41" s="13">
-        <f t="shared" ref="BI41:BL56" si="27">(1-BE5)/(BI5+1-BE5)</f>
+        <f t="shared" ref="BI41:BL56" si="36">(1-BE5)/(BI5+1-BE5)</f>
         <v>0.31929046563192903</v>
       </c>
       <c r="BJ41" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.57539682539682546</v>
       </c>
       <c r="BK41" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.80645161290322587</v>
       </c>
       <c r="BL41" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.25</v>
       </c>
       <c r="BM41" s="45"/>
@@ -15470,7 +15370,7 @@
         <f t="shared" si="24"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP42" s="80">
+      <c r="AP42" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -15512,35 +15412,35 @@
         <v>2</v>
       </c>
       <c r="BE42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BF42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.1103678929765886</v>
       </c>
       <c r="BG42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BH42" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>6.3897763578275226E-3</v>
       </c>
       <c r="BJ42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.51839464882943143</v>
       </c>
       <c r="BK42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.48000000000000004</v>
       </c>
       <c r="BL42" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="BM42" s="45"/>
@@ -15622,7 +15522,7 @@
       <c r="Q43" s="5">
         <v>4</v>
       </c>
-      <c r="R43" s="114">
+      <c r="R43" s="89">
         <v>6</v>
       </c>
       <c r="AL43" s="39" t="s">
@@ -15640,7 +15540,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP43" s="80">
+      <c r="AP43" s="79">
         <f t="shared" si="25"/>
         <v>0.66666666666666663</v>
       </c>
@@ -15682,35 +15582,35 @@
         <v>4</v>
       </c>
       <c r="BE43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>4.010695187165772E-2</v>
       </c>
       <c r="BF43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.80208333333333326</v>
       </c>
       <c r="BG43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH43" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI43" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.20855614973262038</v>
       </c>
       <c r="BJ43" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.88020833333333326</v>
       </c>
       <c r="BK43" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="BL43" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM43" s="45"/>
@@ -15765,7 +15665,7 @@
       <c r="Q44" s="5">
         <v>0</v>
       </c>
-      <c r="R44" s="114">
+      <c r="R44" s="89">
         <v>0</v>
       </c>
       <c r="AL44" s="39" t="s">
@@ -15783,7 +15683,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP44" s="80">
+      <c r="AP44" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -15825,35 +15725,35 @@
         <v>5</v>
       </c>
       <c r="BE44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>1.4705882352941131E-2</v>
       </c>
       <c r="BF44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.375</v>
       </c>
       <c r="BG44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH44" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI44" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.10000000000000002</v>
       </c>
       <c r="BJ44" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.63750000000000007</v>
       </c>
       <c r="BK44" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="BL44" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM44" s="45"/>
@@ -15908,7 +15808,7 @@
       <c r="Q45" s="5">
         <v>1</v>
       </c>
-      <c r="R45" s="114">
+      <c r="R45" s="89">
         <v>1</v>
       </c>
       <c r="AL45" s="39" t="s">
@@ -15926,7 +15826,7 @@
         <f t="shared" si="24"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP45" s="80">
+      <c r="AP45" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -15968,35 +15868,35 @@
         <v>6</v>
       </c>
       <c r="BE45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>5.7471264367816119E-2</v>
       </c>
       <c r="BF45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.23605150214592274</v>
       </c>
       <c r="BG45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH45" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI45" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.16379310344827583</v>
       </c>
       <c r="BJ45" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.47639484978540764</v>
       </c>
       <c r="BK45" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL45" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM45" s="45"/>
@@ -16051,7 +15951,7 @@
       <c r="Q46" s="5">
         <v>2</v>
       </c>
-      <c r="R46" s="114">
+      <c r="R46" s="89">
         <v>5</v>
       </c>
       <c r="AL46" s="39" t="s">
@@ -16069,7 +15969,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP46" s="80">
+      <c r="AP46" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16111,35 +16011,35 @@
         <v>8</v>
       </c>
       <c r="BE46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>2.9498525073746323E-2</v>
       </c>
       <c r="BF46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.55825242718446599</v>
       </c>
       <c r="BG46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH46" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI46" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.11209439528023599</v>
       </c>
       <c r="BJ46" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.69902912621359214</v>
       </c>
       <c r="BK46" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.9285714285714286</v>
       </c>
       <c r="BL46" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.25</v>
       </c>
       <c r="BM46" s="45"/>
@@ -16194,7 +16094,7 @@
       <c r="Q47" s="5">
         <v>1</v>
       </c>
-      <c r="R47" s="114">
+      <c r="R47" s="89">
         <v>6</v>
       </c>
       <c r="AL47" s="39" t="s">
@@ -16212,7 +16112,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP47" s="80">
+      <c r="AP47" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16254,35 +16154,35 @@
         <v>9</v>
       </c>
       <c r="BE47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>4.9140049140049158E-2</v>
       </c>
       <c r="BF47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH47" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI47" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.28501228501228504</v>
       </c>
       <c r="BJ47" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.46200607902735558</v>
       </c>
       <c r="BK47" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL47" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.5</v>
       </c>
       <c r="BM47" s="45"/>
@@ -16337,7 +16237,7 @@
       <c r="Q48" s="5">
         <v>2</v>
       </c>
-      <c r="R48" s="114">
+      <c r="R48" s="89">
         <v>1</v>
       </c>
       <c r="AL48" s="39" t="s">
@@ -16355,7 +16255,7 @@
         <f t="shared" si="24"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP48" s="80">
+      <c r="AP48" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16397,35 +16297,35 @@
         <v>10</v>
       </c>
       <c r="BE48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>9.1346153846153855E-2</v>
       </c>
       <c r="BF48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.59605911330049266</v>
       </c>
       <c r="BG48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.5</v>
       </c>
       <c r="BH48" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.15384615384615383</v>
       </c>
       <c r="BI48" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.34375</v>
       </c>
       <c r="BJ48" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.72413793103448276</v>
       </c>
       <c r="BK48" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.73529411764705888</v>
       </c>
       <c r="BL48" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.46153846153846162</v>
       </c>
       <c r="BM48" s="45"/>
@@ -16480,7 +16380,7 @@
       <c r="Q49" s="5">
         <v>15</v>
       </c>
-      <c r="R49" s="114">
+      <c r="R49" s="89">
         <v>9</v>
       </c>
       <c r="AL49" s="39" t="s">
@@ -16498,7 +16398,7 @@
         <f t="shared" si="24"/>
         <v>0.53846153846153844</v>
       </c>
-      <c r="AP49" s="80">
+      <c r="AP49" s="79">
         <f t="shared" si="25"/>
         <v>0.66666666666666663</v>
       </c>
@@ -16540,35 +16440,35 @@
         <v>11</v>
       </c>
       <c r="BE49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BF49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.29147982062780264</v>
       </c>
       <c r="BG49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="BH49" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI49" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>9.5541401273885485E-3</v>
       </c>
       <c r="BJ49" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.49775784753363228</v>
       </c>
       <c r="BK49" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="BL49" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BM49" s="45"/>
@@ -16623,7 +16523,7 @@
       <c r="Q50" s="5">
         <v>1</v>
       </c>
-      <c r="R50" s="114">
+      <c r="R50" s="89">
         <v>0</v>
       </c>
       <c r="AL50" s="39" t="s">
@@ -16641,7 +16541,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP50" s="80">
+      <c r="AP50" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16683,35 +16583,35 @@
         <v>12</v>
       </c>
       <c r="BE50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>1.4681892332789581E-2</v>
       </c>
       <c r="BF50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.44978165938864634</v>
       </c>
       <c r="BG50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="BH50" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.5073409461663948</v>
       </c>
       <c r="BJ50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.67685589519650657</v>
       </c>
       <c r="BK50" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.6097560975609756</v>
       </c>
       <c r="BL50" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.43750000000000006</v>
       </c>
       <c r="BM50" s="45"/>
@@ -16721,7 +16621,7 @@
       <c r="A51" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="B51" s="59" t="s">
+      <c r="B51" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="24">
@@ -16739,7 +16639,7 @@
       <c r="H51" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="I51" s="59" t="s">
+      <c r="I51" s="58" t="s">
         <v>119</v>
       </c>
       <c r="J51" s="24">
@@ -16754,7 +16654,7 @@
       <c r="M51" s="24">
         <v>0</v>
       </c>
-      <c r="N51" s="59" t="s">
+      <c r="N51" s="58" t="s">
         <v>120</v>
       </c>
       <c r="O51" s="24">
@@ -16766,25 +16666,25 @@
       <c r="Q51" s="24">
         <v>8</v>
       </c>
-      <c r="R51" s="115">
-        <v>1</v>
-      </c>
-      <c r="AL51" s="73" t="s">
+      <c r="R51" s="90">
+        <v>1</v>
+      </c>
+      <c r="AL51" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AM51" s="84">
+      <c r="AM51" s="83">
         <f t="shared" si="22"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN51" s="85">
+      <c r="AN51" s="84">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO51" s="85">
+      <c r="AO51" s="84">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP51" s="86">
+      <c r="AP51" s="85">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -16794,31 +16694,31 @@
       <c r="AS51" s="18">
         <v>4</v>
       </c>
-      <c r="AT51" s="60">
-        <v>1</v>
-      </c>
-      <c r="AU51" s="60">
+      <c r="AT51" s="59">
+        <v>1</v>
+      </c>
+      <c r="AU51" s="59">
         <v>0.29943502824858759</v>
       </c>
-      <c r="AV51" s="60">
+      <c r="AV51" s="59">
         <v>0.73076923076923073</v>
       </c>
-      <c r="AW51" s="60">
+      <c r="AW51" s="59">
         <v>0</v>
       </c>
       <c r="AX51" s="18">
         <v>5</v>
       </c>
-      <c r="AY51" s="60">
+      <c r="AY51" s="59">
         <v>0.98713826366559487</v>
       </c>
-      <c r="AZ51" s="60">
+      <c r="AZ51" s="59">
         <v>0.5423728813559322</v>
       </c>
-      <c r="BA51" s="60">
+      <c r="BA51" s="59">
         <v>0.69230769230769229</v>
       </c>
-      <c r="BB51" s="61">
+      <c r="BB51" s="60">
         <v>0.1111111111111111</v>
       </c>
       <c r="BC51" s="45"/>
@@ -16826,35 +16726,35 @@
         <v>13</v>
       </c>
       <c r="BE51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>2.1604938271604934E-2</v>
       </c>
       <c r="BF51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.25523012552301261</v>
       </c>
       <c r="BG51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH51" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI51" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>6.1728395061728419E-2</v>
       </c>
       <c r="BJ51" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.5146443514644351</v>
       </c>
       <c r="BK51" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL51" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.35714285714285715</v>
       </c>
       <c r="BM51" s="45"/>
@@ -16883,19 +16783,19 @@
       <c r="AL52" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM52" s="77">
+      <c r="AM52" s="76">
         <f t="shared" si="22"/>
         <v>0.96784565916398713</v>
       </c>
-      <c r="AN52" s="78">
+      <c r="AN52" s="77">
         <f t="shared" si="23"/>
         <v>0.49717514124293788</v>
       </c>
-      <c r="AO52" s="78">
+      <c r="AO52" s="77">
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP52" s="79">
+      <c r="AP52" s="78">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -16904,35 +16804,35 @@
         <v>14</v>
       </c>
       <c r="BE52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>5.9659090909090898E-2</v>
       </c>
       <c r="BF52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.40092165898617516</v>
       </c>
       <c r="BG52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.92592592592592582</v>
       </c>
       <c r="BH52" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI52" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.17613636363636365</v>
       </c>
       <c r="BJ52" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.58525345622119818</v>
       </c>
       <c r="BK52" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.96296296296296291</v>
       </c>
       <c r="BL52" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.4</v>
       </c>
     </row>
@@ -16971,7 +16871,7 @@
         <f t="shared" si="24"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP53" s="80">
+      <c r="AP53" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -16980,35 +16880,35 @@
         <v>15</v>
       </c>
       <c r="BE53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>9.4339622641509569E-3</v>
       </c>
       <c r="BF53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.4358974358974359</v>
       </c>
       <c r="BG53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH53" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI53" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>3.1446540880503158E-2</v>
       </c>
       <c r="BJ53" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.67948717948717952</v>
       </c>
       <c r="BK53" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.89655172413793105</v>
       </c>
       <c r="BL53" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -17047,7 +16947,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP54" s="80">
+      <c r="AP54" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17056,35 +16956,35 @@
         <v>16</v>
       </c>
       <c r="BE54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>9.3596059113300503E-2</v>
       </c>
       <c r="BF54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.40350877192982459</v>
       </c>
       <c r="BG54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.27500000000000008</v>
       </c>
       <c r="BH54" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.125</v>
       </c>
       <c r="BI54" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.32758620689655171</v>
       </c>
       <c r="BJ54" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.62719298245614041</v>
       </c>
       <c r="BK54" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.62500000000000011</v>
       </c>
       <c r="BL54" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.5625</v>
       </c>
     </row>
@@ -17123,7 +17023,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP55" s="80">
+      <c r="AP55" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17132,35 +17032,35 @@
         <v>17</v>
       </c>
       <c r="BE55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>1.2012012012011993E-2</v>
       </c>
       <c r="BF55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.56108597285067874</v>
       </c>
       <c r="BG55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.92592592592592582</v>
       </c>
       <c r="BH55" s="13">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI55" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>7.8078078078078109E-2</v>
       </c>
       <c r="BJ55" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.7601809954751132</v>
       </c>
       <c r="BK55" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.96296296296296291</v>
       </c>
       <c r="BL55" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -17199,7 +17099,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP56" s="80">
+      <c r="AP56" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17208,35 +17108,35 @@
         <v>21</v>
       </c>
       <c r="BE56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BF56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.2967032967032967</v>
       </c>
       <c r="BG56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0.52941176470588236</v>
       </c>
       <c r="BH56" s="54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BI56" s="54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>1.2698412698412683E-2</v>
       </c>
       <c r="BJ56" s="54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.64835164835164838</v>
       </c>
       <c r="BK56" s="54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.76470588235294112</v>
       </c>
       <c r="BL56" s="55">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0.10000000000000003</v>
       </c>
     </row>
@@ -17275,7 +17175,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP57" s="80">
+      <c r="AP57" s="79">
         <f t="shared" si="25"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17316,7 +17216,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP58" s="80">
+      <c r="AP58" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17357,7 +17257,7 @@
         <f t="shared" si="24"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP59" s="80">
+      <c r="AP59" s="79">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -17398,7 +17298,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP60" s="80">
+      <c r="AP60" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17439,7 +17339,7 @@
         <f t="shared" si="24"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP61" s="80">
+      <c r="AP61" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17480,7 +17380,7 @@
         <f t="shared" si="24"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP62" s="80">
+      <c r="AP62" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17521,7 +17421,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP63" s="80">
+      <c r="AP63" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17562,7 +17462,7 @@
         <f t="shared" si="24"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP64" s="80">
+      <c r="AP64" s="79">
         <f t="shared" si="25"/>
         <v>0.77777777777777779</v>
       </c>
@@ -17603,7 +17503,7 @@
         <f t="shared" si="24"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP65" s="80">
+      <c r="AP65" s="79">
         <f t="shared" si="25"/>
         <v>0.55555555555555558</v>
       </c>
@@ -17644,7 +17544,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP66" s="80">
+      <c r="AP66" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
@@ -17685,49 +17585,49 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP67" s="80">
+      <c r="AP67" s="79">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="AR67" s="4"/>
     </row>
     <row r="68" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="73" t="s">
+      <c r="A68" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="75">
+      <c r="B68" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="74">
         <v>18</v>
       </c>
-      <c r="D68" s="75">
+      <c r="D68" s="74">
         <v>107</v>
       </c>
-      <c r="E68" s="75">
+      <c r="E68" s="74">
         <v>2</v>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="75">
         <v>3</v>
       </c>
       <c r="H68" s="4"/>
       <c r="AL68" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="AM68" s="81">
-        <f t="shared" ref="AM68:AM99" si="28">(AG$4-C68)/(AG$4-AG$5)</f>
+      <c r="AM68" s="80">
+        <f t="shared" ref="AM68:AM99" si="37">(AG$4-C68)/(AG$4-AG$5)</f>
         <v>0.94212218649517687</v>
       </c>
-      <c r="AN68" s="82">
-        <f t="shared" ref="AN68:AN99" si="29">(D68-AH$5)/(AH$4-AH$5)</f>
+      <c r="AN68" s="81">
+        <f t="shared" ref="AN68:AN99" si="38">(D68-AH$5)/(AH$4-AH$5)</f>
         <v>0.60451977401129942</v>
       </c>
-      <c r="AO68" s="82">
-        <f t="shared" ref="AO68:AO99" si="30">(E68-AI$5)/(AI$4-AI$5)</f>
+      <c r="AO68" s="81">
+        <f t="shared" ref="AO68:AO99" si="39">(E68-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP68" s="83">
-        <f t="shared" ref="AP68:AP99" si="31">(AJ$4-F68)/(AJ$4-AJ$5)</f>
+      <c r="AP68" s="82">
+        <f t="shared" ref="AP68:AP99" si="40">(AJ$4-F68)/(AJ$4-AJ$5)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR68" s="4"/>
@@ -17736,39 +17636,39 @@
       <c r="A69" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B69" s="70" t="s">
+      <c r="B69" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="71">
-        <v>1</v>
-      </c>
-      <c r="D69" s="71">
+      <c r="C69" s="70">
+        <v>1</v>
+      </c>
+      <c r="D69" s="70">
         <v>144</v>
       </c>
-      <c r="E69" s="71">
+      <c r="E69" s="70">
         <v>3</v>
       </c>
-      <c r="F69" s="72">
+      <c r="F69" s="71">
         <v>1</v>
       </c>
       <c r="H69" s="4"/>
       <c r="AL69" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="AM69" s="87">
-        <f t="shared" si="28"/>
+      <c r="AM69" s="86">
+        <f t="shared" si="37"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN69" s="88">
-        <f t="shared" si="29"/>
+      <c r="AN69" s="87">
+        <f t="shared" si="38"/>
         <v>0.81355932203389836</v>
       </c>
-      <c r="AO69" s="88">
-        <f t="shared" si="30"/>
+      <c r="AO69" s="87">
+        <f t="shared" si="39"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP69" s="89">
-        <f t="shared" si="31"/>
+      <c r="AP69" s="88">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR69" s="4"/>
@@ -17797,19 +17697,19 @@
         <v>4</v>
       </c>
       <c r="AM70" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.74919614147909963</v>
       </c>
       <c r="AN70" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.12994350282485875</v>
       </c>
       <c r="AO70" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP70" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP70" s="79">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR70" s="4"/>
@@ -17838,19 +17738,19 @@
         <v>5</v>
       </c>
       <c r="AM71" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.89389067524115751</v>
       </c>
       <c r="AN71" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.49152542372881358</v>
       </c>
       <c r="AO71" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP71" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP71" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR71" s="4"/>
@@ -17879,19 +17779,19 @@
         <v>6</v>
       </c>
       <c r="AM72" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.90353697749196138</v>
       </c>
       <c r="AN72" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.4463276836158192</v>
       </c>
       <c r="AO72" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP72" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP72" s="79">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR72" s="4"/>
@@ -17920,19 +17820,19 @@
         <v>8</v>
       </c>
       <c r="AM73" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="AN73" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="AO73" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP73" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP73" s="79">
+        <f t="shared" si="40"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR73" s="4"/>
@@ -17961,19 +17861,19 @@
         <v>9</v>
       </c>
       <c r="AM74" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.6463022508038585</v>
       </c>
       <c r="AN74" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="AO74" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP74" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP74" s="79">
+        <f t="shared" si="40"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AR74" s="4"/>
@@ -18002,19 +17902,19 @@
         <v>10</v>
       </c>
       <c r="AM75" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.54019292604501612</v>
       </c>
       <c r="AN75" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="AO75" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP75" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP75" s="79">
+        <f t="shared" si="40"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR75" s="4"/>
@@ -18043,19 +17943,19 @@
         <v>11</v>
       </c>
       <c r="AM76" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.99678456591639875</v>
       </c>
       <c r="AN76" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="AO76" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP76" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP76" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR76" s="4"/>
@@ -18084,19 +17984,19 @@
         <v>12</v>
       </c>
       <c r="AM77" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.93890675241157562</v>
       </c>
       <c r="AN77" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="AO77" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP77" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP77" s="79">
+        <f t="shared" si="40"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR77" s="4"/>
@@ -18125,19 +18025,19 @@
         <v>13</v>
       </c>
       <c r="AM78" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.93890675241157562</v>
       </c>
       <c r="AN78" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="AO78" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP78" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP78" s="79">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR78" s="4"/>
@@ -18166,19 +18066,19 @@
         <v>14</v>
       </c>
       <c r="AM79" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.80064308681672025</v>
       </c>
       <c r="AN79" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.38983050847457629</v>
       </c>
       <c r="AO79" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP79" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP79" s="79">
+        <f t="shared" si="40"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR79" s="4"/>
@@ -18207,19 +18107,19 @@
         <v>15</v>
       </c>
       <c r="AM80" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="AN80" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.42372881355932202</v>
       </c>
       <c r="AO80" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP80" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP80" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR80" s="4"/>
@@ -18248,19 +18148,19 @@
         <v>16</v>
       </c>
       <c r="AM81" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.6913183279742765</v>
       </c>
       <c r="AN81" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.48022598870056499</v>
       </c>
       <c r="AO81" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP81" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP81" s="79">
+        <f t="shared" si="40"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AR81" s="4"/>
@@ -18289,19 +18189,19 @@
         <v>17</v>
       </c>
       <c r="AM82" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="AN82" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.29943502824858759</v>
       </c>
       <c r="AO82" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP82" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP82" s="79">
+        <f t="shared" si="40"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR82" s="4"/>
@@ -18310,7 +18210,7 @@
       <c r="A83" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="B83" s="59" t="s">
+      <c r="B83" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="24">
@@ -18326,23 +18226,23 @@
         <v>0</v>
       </c>
       <c r="H83" s="4"/>
-      <c r="AL83" s="73" t="s">
+      <c r="AL83" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="AM83" s="84">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="AN83" s="85">
-        <f t="shared" si="29"/>
+      <c r="AM83" s="83">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="AN83" s="84">
+        <f t="shared" si="38"/>
         <v>0.29943502824858759</v>
       </c>
-      <c r="AO83" s="85">
-        <f t="shared" si="30"/>
+      <c r="AO83" s="84">
+        <f t="shared" si="39"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP83" s="86">
-        <f t="shared" si="31"/>
+      <c r="AP83" s="85">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR83" s="4"/>
@@ -18370,20 +18270,20 @@
       <c r="AL84" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AM84" s="77">
-        <f t="shared" si="28"/>
+      <c r="AM84" s="76">
+        <f t="shared" si="37"/>
         <v>0.98392282958199362</v>
       </c>
-      <c r="AN84" s="78">
-        <f t="shared" si="29"/>
+      <c r="AN84" s="77">
+        <f t="shared" si="38"/>
         <v>0.39548022598870058</v>
       </c>
-      <c r="AO84" s="78">
-        <f t="shared" si="30"/>
+      <c r="AO84" s="77">
+        <f t="shared" si="39"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP84" s="79">
-        <f t="shared" si="31"/>
+      <c r="AP84" s="78">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR84" s="4"/>
@@ -18412,19 +18312,19 @@
         <v>2</v>
       </c>
       <c r="AM85" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.99356913183279738</v>
       </c>
       <c r="AN85" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.3559322033898305</v>
       </c>
       <c r="AO85" s="44">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="AP85" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>1</v>
+      </c>
+      <c r="AP85" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR85" s="4"/>
@@ -18453,19 +18353,19 @@
         <v>4</v>
       </c>
       <c r="AM86" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.909967845659164</v>
       </c>
       <c r="AN86" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>7.909604519774012E-2</v>
       </c>
       <c r="AO86" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP86" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP86" s="79">
+        <f t="shared" si="40"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR86" s="4"/>
@@ -18494,19 +18394,19 @@
         <v>5</v>
       </c>
       <c r="AM87" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.909967845659164</v>
       </c>
       <c r="AN87" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="AO87" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP87" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP87" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR87" s="4"/>
@@ -18535,19 +18435,19 @@
         <v>6</v>
       </c>
       <c r="AM88" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.83601286173633438</v>
       </c>
       <c r="AN88" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="AO88" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP88" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP88" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR88" s="4"/>
@@ -18576,19 +18476,19 @@
         <v>8</v>
       </c>
       <c r="AM89" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN89" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.1864406779661017</v>
       </c>
       <c r="AO89" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP89" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP89" s="79">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR89" s="4"/>
@@ -18617,19 +18517,19 @@
         <v>9</v>
       </c>
       <c r="AM90" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.62700964630225076</v>
       </c>
       <c r="AN90" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.22598870056497175</v>
       </c>
       <c r="AO90" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP90" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP90" s="79">
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AR90" s="4"/>
@@ -18658,19 +18558,19 @@
         <v>10</v>
       </c>
       <c r="AM91" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.65273311897106112</v>
       </c>
       <c r="AN91" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="AO91" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP91" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP91" s="79">
+        <f t="shared" si="40"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR91" s="4"/>
@@ -18699,19 +18599,19 @@
         <v>11</v>
       </c>
       <c r="AM92" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="AN92" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.40677966101694918</v>
       </c>
       <c r="AO92" s="44">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AP92" s="80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AP92" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR92" s="4"/>
@@ -18740,19 +18640,19 @@
         <v>12</v>
       </c>
       <c r="AM93" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="AN93" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.21468926553672316</v>
       </c>
       <c r="AO93" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP93" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP93" s="79">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR93" s="4"/>
@@ -18781,19 +18681,19 @@
         <v>13</v>
       </c>
       <c r="AM94" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN94" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.33898305084745761</v>
       </c>
       <c r="AO94" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP94" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP94" s="79">
+        <f t="shared" si="40"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AR94" s="4"/>
@@ -18822,19 +18722,19 @@
         <v>14</v>
       </c>
       <c r="AM95" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.83279742765273312</v>
       </c>
       <c r="AN95" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.50847457627118642</v>
       </c>
       <c r="AO95" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP95" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP95" s="79">
+        <f t="shared" si="40"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR95" s="4"/>
@@ -18863,19 +18763,19 @@
         <v>15</v>
       </c>
       <c r="AM96" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="AN96" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.1751412429378531</v>
       </c>
       <c r="AO96" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP96" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP96" s="79">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR96" s="4"/>
@@ -18904,19 +18804,19 @@
         <v>16</v>
       </c>
       <c r="AM97" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.74598070739549838</v>
       </c>
       <c r="AN97" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.29378531073446329</v>
       </c>
       <c r="AO97" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>0.57692307692307687</v>
       </c>
-      <c r="AP97" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP97" s="79">
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AR97" s="4"/>
@@ -18945,19 +18845,19 @@
         <v>17</v>
       </c>
       <c r="AM98" s="43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>0.96141479099678462</v>
       </c>
       <c r="AN98" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="38"/>
         <v>0.1751412429378531</v>
       </c>
       <c r="AO98" s="44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="39"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP98" s="80">
-        <f t="shared" si="31"/>
+      <c r="AP98" s="79">
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="AR98" s="4"/>
@@ -18966,7 +18866,7 @@
       <c r="A99" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="B99" s="59" t="s">
+      <c r="B99" s="58" t="s">
         <v>21</v>
       </c>
       <c r="C99" s="24">
@@ -18985,44 +18885,26 @@
       <c r="AL99" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="AM99" s="81">
-        <f t="shared" si="28"/>
+      <c r="AM99" s="80">
+        <f t="shared" si="37"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN99" s="82">
-        <f t="shared" si="29"/>
+      <c r="AN99" s="81">
+        <f t="shared" si="38"/>
         <v>0.5423728813559322</v>
       </c>
-      <c r="AO99" s="82">
-        <f t="shared" si="30"/>
+      <c r="AO99" s="81">
+        <f t="shared" si="39"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="AP99" s="83">
-        <f t="shared" si="31"/>
+      <c r="AP99" s="82">
+        <f t="shared" si="40"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR99" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="BD39:BD40"/>
-    <mergeCell ref="BE39:BH39"/>
-    <mergeCell ref="BI39:BL39"/>
-    <mergeCell ref="BP23:BQ23"/>
-    <mergeCell ref="BR23:BS23"/>
-    <mergeCell ref="BT23:BU23"/>
-    <mergeCell ref="BV23:BW23"/>
-    <mergeCell ref="BP25:BQ25"/>
-    <mergeCell ref="BR25:BS25"/>
-    <mergeCell ref="BT25:BU25"/>
-    <mergeCell ref="BV25:BW25"/>
-    <mergeCell ref="BP5:BQ5"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="BT5:BU5"/>
-    <mergeCell ref="BV5:BW5"/>
-    <mergeCell ref="BD21:BD22"/>
-    <mergeCell ref="BE21:BH21"/>
-    <mergeCell ref="BI21:BL21"/>
     <mergeCell ref="CP3:CQ3"/>
     <mergeCell ref="CO1:CS1"/>
     <mergeCell ref="BV3:BW3"/>
@@ -19033,6 +18915,24 @@
     <mergeCell ref="BP3:BQ3"/>
     <mergeCell ref="BR3:BS3"/>
     <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="BP5:BQ5"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="BT5:BU5"/>
+    <mergeCell ref="BV5:BW5"/>
+    <mergeCell ref="BD21:BD22"/>
+    <mergeCell ref="BE21:BH21"/>
+    <mergeCell ref="BI21:BL21"/>
+    <mergeCell ref="BT23:BU23"/>
+    <mergeCell ref="BV23:BW23"/>
+    <mergeCell ref="BP25:BQ25"/>
+    <mergeCell ref="BR25:BS25"/>
+    <mergeCell ref="BT25:BU25"/>
+    <mergeCell ref="BV25:BW25"/>
+    <mergeCell ref="BD39:BD40"/>
+    <mergeCell ref="BE39:BH39"/>
+    <mergeCell ref="BI39:BL39"/>
+    <mergeCell ref="BP23:BQ23"/>
+    <mergeCell ref="BR23:BS23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
